--- a/data/UOL_Separated_All_Activity_Data_Cleaned.xlsx
+++ b/data/UOL_Separated_All_Activity_Data_Cleaned.xlsx
@@ -2,34 +2,35 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" r:id="R90f3fb231bd749ed"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="All Separated Activities" sheetId="2" r:id="Ra352baa02fcf4c8a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Alumni Talk - Mentoring" sheetId="3" r:id="R7fffaa44151e44ed"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Community Engagement" sheetId="4" r:id="R7bf7d7bdd72147d1"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Conference" sheetId="5" r:id="Rd999d50dafd54e4e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Curriculum Feedback Session" sheetId="6" r:id="Rc26a2748e0e84efb"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="GLIT" sheetId="7" r:id="Re6f44ec28ebd4629"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Guest Lecture" sheetId="8" r:id="R6e6709ca4eca4253"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IAB Meeting - Industry Consulta" sheetId="9" r:id="R60b1d24e70e04f42"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IP" sheetId="10" r:id="Rb7e70aa09f014e0c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IV" sheetId="11" r:id="R830d18e4ba6d4ad0"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Industrial Visit" sheetId="12" r:id="R3f68e311bb0543b4"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Internship-Placement" sheetId="13" r:id="R279f07b1ce5b4fef"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="MOU" sheetId="14" r:id="R5d5b5f5530194cdc"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="MoU Signing (Memorandum of Unde" sheetId="15" r:id="R1de5a835bb1a41b7"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Others" sheetId="16" r:id="R7ee6ca0d2fab4f32"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Research Collaboration" sheetId="17" r:id="Rc10f2b4f0df749db"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Seminar" sheetId="18" r:id="R7d311f7f12f14de4"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Unclassified" sheetId="19" r:id="R697b2e27210646f1"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Workshop" sheetId="20" r:id="Rff3b3dd474774c81"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Guest Lecture - GLIT" sheetId="21" r:id="R4a2b6251d6f246a9"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Industrial Visit - IV" sheetId="22" r:id="R886bfcc2e4204bc3"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Internship - Placement" sheetId="23" r:id="R21da689a672e4641"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="MoU - MoU Signing" sheetId="24" r:id="R6ac1a8e0d609417b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="New Data Added" sheetId="25" r:id="R7b1438ed3e7f44e8"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Planned - Section 4" sheetId="26" r:id="R61a7f2e6836c4d11"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Planned Activities" sheetId="27" r:id="R92936daee94f410d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Remote Activities" sheetId="28" r:id="R3026b5b11c304ba5"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" r:id="R40c7aae60b6f4c2a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="All Separated Activities" sheetId="2" r:id="Rd652f22d5fa141fb"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Alumni Talk - Mentoring" sheetId="3" r:id="R7f13629bc35949ed"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Community Engagement" sheetId="4" r:id="Rcd9469b5aa6b48dc"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Conference" sheetId="5" r:id="Rb73745989755437e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Curriculum Feedback Session" sheetId="6" r:id="R13a3d60c9e4041c7"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="GLIT" sheetId="7" r:id="R73e76bfe497542a5"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Guest Lecture" sheetId="8" r:id="R1804a3d67e1545c6"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IAB Meeting - Industry Consulta" sheetId="9" r:id="R226ed53d53a54fac"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IP" sheetId="10" r:id="R4d2607462a4f4201"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IV" sheetId="11" r:id="R5eeaa0b3e68847b8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Industrial Visit" sheetId="12" r:id="R01755d1d20c4490e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Internship-Placement" sheetId="13" r:id="Rf0f9af1a750e4520"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="MOU" sheetId="14" r:id="Rac36945a0b0d4b3d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="MoU Signing (Memorandum of Unde" sheetId="15" r:id="R27c6e24865c04a86"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Others" sheetId="16" r:id="Rb4c5a61e5dcb46c5"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Research Collaboration" sheetId="17" r:id="R000b393cb4034258"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Seminar" sheetId="18" r:id="Rdc66917cc3914cb8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Unclassified" sheetId="19" r:id="R8af39c668b464505"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Workshop" sheetId="20" r:id="R24d052078dbb4024"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Guest Lecture - GLIT" sheetId="21" r:id="Rfa036c4d5df64537"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Industrial Visit - IV" sheetId="22" r:id="R485bba58ffc94320"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Internship - Placement" sheetId="23" r:id="R424a9a7d9a3a455b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="MoU - MoU Signing" sheetId="24" r:id="R3d857b6c059c4f8e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="New Data Added" sheetId="25" r:id="R2cc8a0cf3f964cf1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Planned - Section 4" sheetId="26" r:id="R5c3a474c68f441eb"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Planned Activities" sheetId="27" r:id="Rf88c499b5e014908"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Remote Activities" sheetId="28" r:id="R1281ecdb529e42c4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="64 Submission Reconciliation" sheetId="29" r:id="R37e94136759f47d3"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -1453,7 +1454,7 @@
       <x:name val="Carlito"/>
     </x:font>
   </x:fonts>
-  <x:fills count="14">
+  <x:fills count="15">
     <x:fill>
       <x:patternFill patternType="none"/>
     </x:fill>
@@ -1520,6 +1521,11 @@
         <x:fgColor rgb="FFD9EAF7"/>
       </x:patternFill>
     </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF113A54"/>
+      </x:patternFill>
+    </x:fill>
   </x:fills>
   <x:borders count="20">
     <x:border/>
@@ -1546,7 +1552,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="65">
+  <x:cellXfs count="67">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <x:alignment wrapText="1"/>
@@ -1690,6 +1696,8 @@
     <x:xf numFmtId="0" fontId="1" fillId="12" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="center" vertical="center" wrapText="1"/>
     </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="14" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="1" fillId="14" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </x:cellXfs>
   <x:cellStyles count="1">
     <x:cellStyle name="Normal" xfId="0"/>
@@ -11147,42 +11155,106 @@
       </x:c>
     </x:row>
     <x:row r="9">
-      <x:c r="A9" s="2"/>
-      <x:c r="B9" s="2"/>
-      <x:c r="C9" s="2"/>
-      <x:c r="D9" s="2"/>
-      <x:c r="E9" s="2"/>
-      <x:c r="F9" s="2"/>
-      <x:c r="G9" s="2"/>
-      <x:c r="H9" s="2"/>
-      <x:c r="I9" s="2"/>
-      <x:c r="J9" s="2"/>
-      <x:c r="K9" s="2"/>
-      <x:c r="L9" s="2"/>
-      <x:c r="M9" s="2"/>
-      <x:c r="N9" s="2"/>
-      <x:c r="O9" s="2"/>
-      <x:c r="P9" s="2"/>
-      <x:c r="Q9" s="2"/>
+      <x:c r="A9" s="2" t="str">
+        <x:v>PRPSTFPT103</x:v>
+      </x:c>
+      <x:c r="B9" s="2" t="str">
+        <x:v>Foc Soca Lhr</x:v>
+      </x:c>
+      <x:c r="C9" s="2" t="str">
+        <x:v>Pending From Linkage Officer</x:v>
+      </x:c>
+      <x:c r="D9" s="2" t="str">
+        <x:v>7 October 2026</x:v>
+      </x:c>
+      <x:c r="E9" s="2" t="str">
+        <x:v>2026-12</x:v>
+      </x:c>
+      <x:c r="F9" s="2" t="str">
+        <x:v>Lahore Campus</x:v>
+      </x:c>
+      <x:c r="G9" s="2" t="str">
+        <x:v>Faculty of Arts and Architecture</x:v>
+      </x:c>
+      <x:c r="H9" s="2" t="str">
+        <x:v>School of Creative Arts</x:v>
+      </x:c>
+      <x:c r="I9" s="2" t="str">
+        <x:v>Foc Soca Lhr</x:v>
+      </x:c>
+      <x:c r="J9" s="2" t="str"/>
+      <x:c r="K9" s="2" t="str">
+        <x:v>Others</x:v>
+      </x:c>
+      <x:c r="L9" s="2" t="str">
+        <x:v>Others</x:v>
+      </x:c>
+      <x:c r="M9" s="2" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="N9" s="2" t="str">
+        <x:v>Lahore Safe City Blood Bank</x:v>
+      </x:c>
+      <x:c r="O9" s="2" t="str">
+        <x:v>Yes</x:v>
+      </x:c>
+      <x:c r="P9" s="2" t="str">
+        <x:v>Yes</x:v>
+      </x:c>
+      <x:c r="Q9" s="2" t="str">
+        <x:v>Blood Donation  Awareness Campaign</x:v>
+      </x:c>
     </x:row>
     <x:row r="10">
-      <x:c r="A10" s="2"/>
-      <x:c r="B10" s="2"/>
-      <x:c r="C10" s="2"/>
-      <x:c r="D10" s="2"/>
-      <x:c r="E10" s="2"/>
-      <x:c r="F10" s="2"/>
-      <x:c r="G10" s="2"/>
-      <x:c r="H10" s="2"/>
-      <x:c r="I10" s="2"/>
-      <x:c r="J10" s="2"/>
-      <x:c r="K10" s="2"/>
-      <x:c r="L10" s="2"/>
-      <x:c r="M10" s="2"/>
-      <x:c r="N10" s="2"/>
-      <x:c r="O10" s="2"/>
-      <x:c r="P10" s="2"/>
-      <x:c r="Q10" s="2"/>
+      <x:c r="A10" s="2" t="str">
+        <x:v>PRPSTFPT43</x:v>
+      </x:c>
+      <x:c r="B10" s="2" t="str">
+        <x:v>Foc Doim Lhr</x:v>
+      </x:c>
+      <x:c r="C10" s="2" t="str">
+        <x:v>Pending From Linkage Officer</x:v>
+      </x:c>
+      <x:c r="D10" s="2" t="str">
+        <x:v>21 July 2026</x:v>
+      </x:c>
+      <x:c r="E10" s="2" t="str">
+        <x:v>2026-06</x:v>
+      </x:c>
+      <x:c r="F10" s="2" t="str">
+        <x:v>Lahore Campus</x:v>
+      </x:c>
+      <x:c r="G10" s="2" t="str">
+        <x:v>Faculty of Management Sciences</x:v>
+      </x:c>
+      <x:c r="H10" s="2" t="str">
+        <x:v>Department of Information Management</x:v>
+      </x:c>
+      <x:c r="I10" s="2" t="str">
+        <x:v>Foc Doim Lhr</x:v>
+      </x:c>
+      <x:c r="J10" s="2" t="str"/>
+      <x:c r="K10" s="2" t="str">
+        <x:v>Others</x:v>
+      </x:c>
+      <x:c r="L10" s="2" t="str">
+        <x:v>Others</x:v>
+      </x:c>
+      <x:c r="M10" s="2" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="N10" s="2" t="str">
+        <x:v>Department of Information Management (DoIM) UOL</x:v>
+      </x:c>
+      <x:c r="O10" s="2" t="str">
+        <x:v>Yes</x:v>
+      </x:c>
+      <x:c r="P10" s="2" t="str">
+        <x:v>Yes</x:v>
+      </x:c>
+      <x:c r="Q10" s="2" t="str">
+        <x:v>Student Poster Exhibition and Competition 2026 at The Department of Information Management &amp; Completion of Batch Spring 2026 First Semester, and 2nd Semester by Batch Fall 2025. To promoted research culture and academic creativity among students  and	strengthened research communication and poster presentation skills. Activity Concluded.</x:v>
+      </x:c>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -12531,23 +12603,55 @@
       </x:c>
     </x:row>
     <x:row r="26">
-      <x:c r="A26" s="2"/>
-      <x:c r="B26" s="2"/>
-      <x:c r="C26" s="2"/>
-      <x:c r="D26" s="2"/>
-      <x:c r="E26" s="2"/>
-      <x:c r="F26" s="2"/>
-      <x:c r="G26" s="2"/>
-      <x:c r="H26" s="2"/>
-      <x:c r="I26" s="2"/>
-      <x:c r="J26" s="2"/>
-      <x:c r="K26" s="2"/>
-      <x:c r="L26" s="2"/>
-      <x:c r="M26" s="2"/>
-      <x:c r="N26" s="2"/>
-      <x:c r="O26" s="2"/>
-      <x:c r="P26" s="2"/>
-      <x:c r="Q26" s="2"/>
+      <x:c r="A26" s="2" t="str">
+        <x:v>PRPSTFPT74</x:v>
+      </x:c>
+      <x:c r="B26" s="2" t="str">
+        <x:v>Foc Uifsrt Lhr</x:v>
+      </x:c>
+      <x:c r="C26" s="2" t="str">
+        <x:v>Pending From Linkage Officer</x:v>
+      </x:c>
+      <x:c r="D26" s="2" t="str">
+        <x:v>31 July 2026</x:v>
+      </x:c>
+      <x:c r="E26" s="2" t="str">
+        <x:v>2026-04</x:v>
+      </x:c>
+      <x:c r="F26" s="2" t="str">
+        <x:v>Lahore Campus</x:v>
+      </x:c>
+      <x:c r="G26" s="2" t="str">
+        <x:v>Faculty of Allied Health Sciences</x:v>
+      </x:c>
+      <x:c r="H26" s="2" t="str">
+        <x:v>University Institute of Food Science &amp; Technology</x:v>
+      </x:c>
+      <x:c r="I26" s="2" t="str">
+        <x:v>Foc Uifsrt Lhr</x:v>
+      </x:c>
+      <x:c r="J26" s="2" t="str"/>
+      <x:c r="K26" s="2" t="str">
+        <x:v>Research Collaboration</x:v>
+      </x:c>
+      <x:c r="L26" s="2" t="str">
+        <x:v>Research Collaboration</x:v>
+      </x:c>
+      <x:c r="M26" s="2" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="N26" s="2" t="str">
+        <x:v>Punjab Agriculture &amp; Meat Company (PAMCO)</x:v>
+      </x:c>
+      <x:c r="O26" s="2" t="str">
+        <x:v>Yes</x:v>
+      </x:c>
+      <x:c r="P26" s="2" t="str">
+        <x:v>Yes</x:v>
+      </x:c>
+      <x:c r="Q26" s="2" t="str">
+        <x:v>Gained Practical Knowledge</x:v>
+      </x:c>
     </x:row>
     <x:row r="27">
       <x:c r="A27" s="2"/>
@@ -14017,6 +14121,310 @@
         <x:v>45</x:v>
       </x:c>
     </x:row>
+    <x:row r="29">
+      <x:c r="A29" t="str">
+        <x:v>PRPSTFPT103</x:v>
+      </x:c>
+      <x:c r="B29" t="str">
+        <x:v>Foc Soca Lhr</x:v>
+      </x:c>
+      <x:c r="C29" t="str">
+        <x:v>Pending From Linkage Officer</x:v>
+      </x:c>
+      <x:c r="D29" t="str">
+        <x:v>7 October 2026</x:v>
+      </x:c>
+      <x:c r="E29"/>
+      <x:c r="F29" t="str">
+        <x:v>Lahore Campus</x:v>
+      </x:c>
+      <x:c r="G29" t="str">
+        <x:v>Faculty of Arts and Architecture</x:v>
+      </x:c>
+      <x:c r="H29" t="str">
+        <x:v>School of Creative Arts</x:v>
+      </x:c>
+      <x:c r="I29" t="str">
+        <x:v>Foc Soca Lhr</x:v>
+      </x:c>
+      <x:c r="J29" t="str"/>
+      <x:c r="K29" t="str">
+        <x:v>Seminar</x:v>
+      </x:c>
+      <x:c r="L29" t="str">
+        <x:v>Seminar / Conference / Workshop</x:v>
+      </x:c>
+      <x:c r="M29" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="N29" t="str">
+        <x:v>Industrial Option SMEDA SMEDA Small and Medium Enterprises Development Authority</x:v>
+      </x:c>
+      <x:c r="O29" t="str">
+        <x:v>Yes</x:v>
+      </x:c>
+      <x:c r="P29" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="Q29" t="str">
+        <x:v>Planned</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="30">
+      <x:c r="A30" t="str">
+        <x:v>PRPSTFPT96</x:v>
+      </x:c>
+      <x:c r="B30" t="str">
+        <x:v>Foc Soa Lhr</x:v>
+      </x:c>
+      <x:c r="C30" t="str">
+        <x:v>Pending From Linkage Officer</x:v>
+      </x:c>
+      <x:c r="D30" t="str">
+        <x:v>1 October 2026</x:v>
+      </x:c>
+      <x:c r="E30" t="str">
+        <x:v>2026-09</x:v>
+      </x:c>
+      <x:c r="F30" t="str">
+        <x:v>Lahore Campus</x:v>
+      </x:c>
+      <x:c r="G30" t="str">
+        <x:v>Faculty of Arts and Architecture</x:v>
+      </x:c>
+      <x:c r="H30" t="str">
+        <x:v>School of Architecture</x:v>
+      </x:c>
+      <x:c r="I30" t="str">
+        <x:v>Foc Soa Lhr</x:v>
+      </x:c>
+      <x:c r="J30" t="str"/>
+      <x:c r="K30" t="str">
+        <x:v>Seminar</x:v>
+      </x:c>
+      <x:c r="L30" t="str">
+        <x:v>Seminar / Conference / Workshop</x:v>
+      </x:c>
+      <x:c r="M30" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="N30" t="str">
+        <x:v>Institute of Architects of Pakistan IAP</x:v>
+      </x:c>
+      <x:c r="O30" t="str">
+        <x:v>Yes</x:v>
+      </x:c>
+      <x:c r="P30" t="str">
+        <x:v>Yes</x:v>
+      </x:c>
+      <x:c r="Q30" t="str">
+        <x:v>A day of ideas, conversations, and new possibilities around AI and the future of architecture in Pakistan.  From thought-provoking discussions to meaningful exchanges, “AI &amp; The Future of Architecture in Pakistan” brought together architects, educators, students, and design thinkers to explore how technology is reshaping the way we imagine and create our built environment.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="31">
+      <x:c r="A31" t="str">
+        <x:v>PRPSTFPT43</x:v>
+      </x:c>
+      <x:c r="B31" t="str">
+        <x:v>Foc Doim Lhr</x:v>
+      </x:c>
+      <x:c r="C31" t="str">
+        <x:v>Pending From Linkage Officer</x:v>
+      </x:c>
+      <x:c r="D31" t="str">
+        <x:v>21 July 2026</x:v>
+      </x:c>
+      <x:c r="E31" t="str">
+        <x:v>2026-06</x:v>
+      </x:c>
+      <x:c r="F31" t="str">
+        <x:v>Lahore Campus</x:v>
+      </x:c>
+      <x:c r="G31" t="str">
+        <x:v>Faculty of Management Sciences</x:v>
+      </x:c>
+      <x:c r="H31" t="str">
+        <x:v>Department of Information Management</x:v>
+      </x:c>
+      <x:c r="I31" t="str">
+        <x:v>Foc Doim Lhr</x:v>
+      </x:c>
+      <x:c r="J31" t="str"/>
+      <x:c r="K31" t="str">
+        <x:v>Seminar</x:v>
+      </x:c>
+      <x:c r="L31" t="str">
+        <x:v>Seminar / Conference / Workshop</x:v>
+      </x:c>
+      <x:c r="M31" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="N31" t="str">
+        <x:v>UK</x:v>
+      </x:c>
+      <x:c r="O31" t="str">
+        <x:v>Yes</x:v>
+      </x:c>
+      <x:c r="P31" t="str">
+        <x:v>Yes</x:v>
+      </x:c>
+      <x:c r="Q31" t="str">
+        <x:v>International Webinar Series 2026; Writing Literature Review Ethically in the Age of AI (Resource Person Yanhua Liu) UK, The webinar aimed to enhance participants’ understanding of effective literature review practices, ethical academic writing, and the responsible use of Artificial Intelligence (AI) in research. Activity Concluded.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="32">
+      <x:c r="A32" t="str">
+        <x:v>PRPSTFPT43</x:v>
+      </x:c>
+      <x:c r="B32" t="str">
+        <x:v>Foc Doim Lhr</x:v>
+      </x:c>
+      <x:c r="C32" t="str">
+        <x:v>Pending From Linkage Officer</x:v>
+      </x:c>
+      <x:c r="D32" t="str">
+        <x:v>21 July 2026</x:v>
+      </x:c>
+      <x:c r="E32" t="str">
+        <x:v>2026-07</x:v>
+      </x:c>
+      <x:c r="F32" t="str">
+        <x:v>Lahore Campus</x:v>
+      </x:c>
+      <x:c r="G32" t="str">
+        <x:v>Faculty of Management Sciences</x:v>
+      </x:c>
+      <x:c r="H32" t="str">
+        <x:v>Department of Information Management</x:v>
+      </x:c>
+      <x:c r="I32" t="str">
+        <x:v>Foc Doim Lhr</x:v>
+      </x:c>
+      <x:c r="J32" t="str"/>
+      <x:c r="K32" t="str">
+        <x:v>Seminar</x:v>
+      </x:c>
+      <x:c r="L32" t="str">
+        <x:v>Seminar / Conference / Workshop</x:v>
+      </x:c>
+      <x:c r="M32" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="N32" t="str">
+        <x:v>Department of Information Management (DoIM) UOL</x:v>
+      </x:c>
+      <x:c r="O32" t="str">
+        <x:v>Yes</x:v>
+      </x:c>
+      <x:c r="P32" t="str">
+        <x:v>Yes</x:v>
+      </x:c>
+      <x:c r="Q32" t="str">
+        <x:v>𝐁𝐞𝐡𝐚𝐯𝐢𝐨𝐫𝐚𝐥 𝐌𝐚𝐧𝐚𝐠𝐞𝐦𝐞𝐧𝐭: 𝐓𝐡𝐞 𝐉𝐨𝐮𝐫𝐧𝐞𝐲 𝐨𝐟 𝐏𝐫𝐨𝐟𝐞𝐬𝐢𝐨𝐧𝐚𝐥 𝐄𝐱𝐜𝐞𝐥𝐞𝐧𝐜𝐞. (Resource Person Prf. Dr. Zaheer Ahmad)An excellent opportunity for library professionals to enhance the attitudes, skills, and behaviors essential for professional success. Activity Concluded.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="33">
+      <x:c r="A33" t="str">
+        <x:v>PRPSTFPT43</x:v>
+      </x:c>
+      <x:c r="B33" t="str">
+        <x:v>Foc Doim Lhr</x:v>
+      </x:c>
+      <x:c r="C33" t="str">
+        <x:v>Pending From Linkage Officer</x:v>
+      </x:c>
+      <x:c r="D33" t="str">
+        <x:v>21 July 2026</x:v>
+      </x:c>
+      <x:c r="E33" t="str">
+        <x:v>2026-07</x:v>
+      </x:c>
+      <x:c r="F33" t="str">
+        <x:v>Lahore Campus</x:v>
+      </x:c>
+      <x:c r="G33" t="str">
+        <x:v>Faculty of Management Sciences</x:v>
+      </x:c>
+      <x:c r="H33" t="str">
+        <x:v>Department of Information Management</x:v>
+      </x:c>
+      <x:c r="I33" t="str">
+        <x:v>Foc Doim Lhr</x:v>
+      </x:c>
+      <x:c r="J33" t="str"/>
+      <x:c r="K33" t="str">
+        <x:v>Seminar</x:v>
+      </x:c>
+      <x:c r="L33" t="str">
+        <x:v>Seminar / Conference / Workshop</x:v>
+      </x:c>
+      <x:c r="M33" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="N33" t="str">
+        <x:v>COMSATS University Islamabad, Lahore Campus</x:v>
+      </x:c>
+      <x:c r="O33" t="str">
+        <x:v>Yes</x:v>
+      </x:c>
+      <x:c r="P33" t="str">
+        <x:v>Yes</x:v>
+      </x:c>
+      <x:c r="Q33" t="str">
+        <x:v>𝐆𝐥𝐨𝐛𝐚𝐥 𝐃𝐢𝐚𝐥𝐨𝐠𝐮𝐞 𝐨𝐧 𝐑𝐞𝐬𝐞𝐚𝐫𝐜𝐡 𝐁𝐞𝐲𝐨𝐧𝐝 𝐁𝐨𝐮𝐧𝐝, This academic dialogue aims to bring together researchers, faculty members, and professionals to explore emerging avenues for international research collaboration, interdisciplinary engagement, and global academic networking. Activity Concluded.𝐚𝐫𝐢𝐞𝐬: 𝐎𝐩𝐩𝐨𝐫𝐭𝐮𝐧𝐢𝐭𝐢𝐞𝐬 𝐟𝐨𝐫 𝐈𝐧𝐭𝐞𝐫𝐧𝐚𝐭𝐢𝐨𝐧𝐚𝐥 𝐂𝐨𝐥𝐥𝐚𝐛𝐨𝐫𝐚𝐭𝐢𝐨𝐧,</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="34">
+      <x:c r="A34" t="str">
+        <x:v>PRPSTFPT43</x:v>
+      </x:c>
+      <x:c r="B34" t="str">
+        <x:v>Foc Doim Lhr</x:v>
+      </x:c>
+      <x:c r="C34" t="str">
+        <x:v>Pending From Linkage Officer</x:v>
+      </x:c>
+      <x:c r="D34" t="str">
+        <x:v>21 July 2026</x:v>
+      </x:c>
+      <x:c r="E34" t="str">
+        <x:v>2026-07</x:v>
+      </x:c>
+      <x:c r="F34" t="str">
+        <x:v>Lahore Campus</x:v>
+      </x:c>
+      <x:c r="G34" t="str">
+        <x:v>Faculty of Management Sciences</x:v>
+      </x:c>
+      <x:c r="H34" t="str">
+        <x:v>Department of Information Management</x:v>
+      </x:c>
+      <x:c r="I34" t="str">
+        <x:v>Foc Doim Lhr</x:v>
+      </x:c>
+      <x:c r="J34" t="str"/>
+      <x:c r="K34" t="str">
+        <x:v>Seminar</x:v>
+      </x:c>
+      <x:c r="L34" t="str">
+        <x:v>Seminar / Conference / Workshop</x:v>
+      </x:c>
+      <x:c r="M34" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="N34" t="str">
+        <x:v>The Pakistan Scientific and Technological Information Centre (PSTIC), Regional Office Lahore</x:v>
+      </x:c>
+      <x:c r="O34" t="str">
+        <x:v>Yes</x:v>
+      </x:c>
+      <x:c r="P34" t="str">
+        <x:v>Yes</x:v>
+      </x:c>
+      <x:c r="Q34" t="str">
+        <x:v>The webinar on Intelligent Literature Reviews: AI Tools, Critical Thinking, and Research Ethics,  Prof. Dr. Zaheer Ahmad, Resource Person, discussed the significance of literature reviews in identifying research gaps and building a strong scholarly foundation. He demonstrated how AI-powered tools can support literature searching, evidence synthesis, summarization, reference management, and academic writing while emphasizing that researchers must apply critical thinking, sound judgment, and ethical practices throughout the research process. He also stressed the importance of verifying AI-generated content, avoiding plagiarism and fabricated citations, and ensuring transparency in the responsible use of AI.</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>
@@ -28905,555 +29313,1469 @@
       </x:c>
     </x:row>
     <x:row r="299">
-      <x:c r="A299"/>
-      <x:c r="B299"/>
-      <x:c r="C299"/>
-      <x:c r="D299"/>
-      <x:c r="E299"/>
-      <x:c r="F299"/>
-      <x:c r="G299"/>
-      <x:c r="H299"/>
-      <x:c r="I299"/>
-      <x:c r="J299"/>
-      <x:c r="K299"/>
-      <x:c r="L299"/>
-      <x:c r="M299"/>
-      <x:c r="N299"/>
-      <x:c r="O299"/>
-      <x:c r="P299"/>
-      <x:c r="Q299"/>
+      <x:c r="A299" t="str">
+        <x:v>PRPSTFPT103</x:v>
+      </x:c>
+      <x:c r="B299" t="str">
+        <x:v>Foc Soca Lhr</x:v>
+      </x:c>
+      <x:c r="C299" t="str">
+        <x:v>Pending From Linkage Officer</x:v>
+      </x:c>
+      <x:c r="D299" t="str">
+        <x:v>7 October 2026</x:v>
+      </x:c>
+      <x:c r="E299" t="str">
+        <x:v>2026-12</x:v>
+      </x:c>
+      <x:c r="F299" t="str">
+        <x:v>Lahore Campus</x:v>
+      </x:c>
+      <x:c r="G299" t="str">
+        <x:v>Faculty of Arts and Architecture</x:v>
+      </x:c>
+      <x:c r="H299" t="str">
+        <x:v>School of Creative Arts</x:v>
+      </x:c>
+      <x:c r="I299" t="str">
+        <x:v>Foc Soca Lhr</x:v>
+      </x:c>
+      <x:c r="J299" t="str"/>
+      <x:c r="K299" t="str">
+        <x:v>MoU / MoU Signing</x:v>
+      </x:c>
+      <x:c r="L299" t="str">
+        <x:v>MoU Signing</x:v>
+      </x:c>
+      <x:c r="M299" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="N299" t="str">
+        <x:v>Interactive Resource Centre</x:v>
+      </x:c>
+      <x:c r="O299" t="str">
+        <x:v>Yes</x:v>
+      </x:c>
+      <x:c r="P299" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="Q299" t="str">
+        <x:v>Inprogress</x:v>
+      </x:c>
     </x:row>
     <x:row r="300">
-      <x:c r="A300"/>
-      <x:c r="B300"/>
-      <x:c r="C300"/>
-      <x:c r="D300"/>
-      <x:c r="E300"/>
-      <x:c r="F300"/>
-      <x:c r="G300"/>
-      <x:c r="H300"/>
-      <x:c r="I300"/>
-      <x:c r="J300"/>
-      <x:c r="K300"/>
-      <x:c r="L300"/>
-      <x:c r="M300"/>
-      <x:c r="N300"/>
-      <x:c r="O300"/>
-      <x:c r="P300"/>
-      <x:c r="Q300"/>
+      <x:c r="A300" t="str">
+        <x:v>PRPSTFPT103</x:v>
+      </x:c>
+      <x:c r="B300" t="str">
+        <x:v>Foc Soca Lhr</x:v>
+      </x:c>
+      <x:c r="C300" t="str">
+        <x:v>Pending From Linkage Officer</x:v>
+      </x:c>
+      <x:c r="D300" t="str">
+        <x:v>7 October 2026</x:v>
+      </x:c>
+      <x:c r="E300" t="str">
+        <x:v>2026-10</x:v>
+      </x:c>
+      <x:c r="F300" t="str">
+        <x:v>Lahore Campus</x:v>
+      </x:c>
+      <x:c r="G300" t="str">
+        <x:v>Faculty of Arts and Architecture</x:v>
+      </x:c>
+      <x:c r="H300" t="str">
+        <x:v>School of Creative Arts</x:v>
+      </x:c>
+      <x:c r="I300" t="str">
+        <x:v>Foc Soca Lhr</x:v>
+      </x:c>
+      <x:c r="J300" t="str"/>
+      <x:c r="K300" t="str">
+        <x:v>Industrial Visit / IV</x:v>
+      </x:c>
+      <x:c r="L300" t="str">
+        <x:v>Industrial Visit</x:v>
+      </x:c>
+      <x:c r="M300" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="N300" t="str">
+        <x:v>Punjab Safe Cities</x:v>
+      </x:c>
+      <x:c r="O300" t="str">
+        <x:v>Yes</x:v>
+      </x:c>
+      <x:c r="P300" t="str">
+        <x:v>Yes</x:v>
+      </x:c>
+      <x:c r="Q300" t="str">
+        <x:v>Planned</x:v>
+      </x:c>
     </x:row>
     <x:row r="301">
-      <x:c r="A301"/>
-      <x:c r="B301"/>
-      <x:c r="C301"/>
-      <x:c r="D301"/>
+      <x:c r="A301" t="str">
+        <x:v>PRPSTFPT103</x:v>
+      </x:c>
+      <x:c r="B301" t="str">
+        <x:v>Foc Soca Lhr</x:v>
+      </x:c>
+      <x:c r="C301" t="str">
+        <x:v>Pending From Linkage Officer</x:v>
+      </x:c>
+      <x:c r="D301" t="str">
+        <x:v>7 October 2026</x:v>
+      </x:c>
       <x:c r="E301"/>
-      <x:c r="F301"/>
-      <x:c r="G301"/>
-      <x:c r="H301"/>
-      <x:c r="I301"/>
-      <x:c r="J301"/>
-      <x:c r="K301"/>
-      <x:c r="L301"/>
-      <x:c r="M301"/>
-      <x:c r="N301"/>
-      <x:c r="O301"/>
-      <x:c r="P301"/>
-      <x:c r="Q301"/>
+      <x:c r="F301" t="str">
+        <x:v>Lahore Campus</x:v>
+      </x:c>
+      <x:c r="G301" t="str">
+        <x:v>Faculty of Arts and Architecture</x:v>
+      </x:c>
+      <x:c r="H301" t="str">
+        <x:v>School of Creative Arts</x:v>
+      </x:c>
+      <x:c r="I301" t="str">
+        <x:v>Foc Soca Lhr</x:v>
+      </x:c>
+      <x:c r="J301" t="str"/>
+      <x:c r="K301" t="str">
+        <x:v>Industrial Visit / IV</x:v>
+      </x:c>
+      <x:c r="L301" t="str">
+        <x:v>Industrial Visit</x:v>
+      </x:c>
+      <x:c r="M301" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="N301" t="str">
+        <x:v>Radio Broadcasting Station Lahore</x:v>
+      </x:c>
+      <x:c r="O301" t="str">
+        <x:v>Yes</x:v>
+      </x:c>
+      <x:c r="P301" t="str">
+        <x:v>Yes</x:v>
+      </x:c>
+      <x:c r="Q301" t="str">
+        <x:v>Inprogress</x:v>
+      </x:c>
     </x:row>
     <x:row r="302">
-      <x:c r="A302"/>
-      <x:c r="B302"/>
-      <x:c r="C302"/>
-      <x:c r="D302"/>
-      <x:c r="E302"/>
-      <x:c r="F302"/>
-      <x:c r="G302"/>
-      <x:c r="H302"/>
-      <x:c r="I302"/>
-      <x:c r="J302"/>
-      <x:c r="K302"/>
-      <x:c r="L302"/>
-      <x:c r="M302"/>
-      <x:c r="N302"/>
-      <x:c r="O302"/>
-      <x:c r="P302"/>
-      <x:c r="Q302"/>
+      <x:c r="A302" t="str">
+        <x:v>PRPSTFPT103</x:v>
+      </x:c>
+      <x:c r="B302" t="str">
+        <x:v>Foc Soca Lhr</x:v>
+      </x:c>
+      <x:c r="C302" t="str">
+        <x:v>Pending From Linkage Officer</x:v>
+      </x:c>
+      <x:c r="D302" t="str">
+        <x:v>7 October 2026</x:v>
+      </x:c>
+      <x:c r="E302" t="str">
+        <x:v>2026-11</x:v>
+      </x:c>
+      <x:c r="F302" t="str">
+        <x:v>Lahore Campus</x:v>
+      </x:c>
+      <x:c r="G302" t="str">
+        <x:v>Faculty of Arts and Architecture</x:v>
+      </x:c>
+      <x:c r="H302" t="str">
+        <x:v>School of Creative Arts</x:v>
+      </x:c>
+      <x:c r="I302" t="str">
+        <x:v>Foc Soca Lhr</x:v>
+      </x:c>
+      <x:c r="J302" t="str"/>
+      <x:c r="K302" t="str">
+        <x:v>Industrial Visit / IV</x:v>
+      </x:c>
+      <x:c r="L302" t="str">
+        <x:v>Industrial Visit</x:v>
+      </x:c>
+      <x:c r="M302" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="N302" t="str">
+        <x:v>Industrial visit to the Directorate General Public Relations</x:v>
+      </x:c>
+      <x:c r="O302" t="str">
+        <x:v>Yes</x:v>
+      </x:c>
+      <x:c r="P302" t="str">
+        <x:v>Yes</x:v>
+      </x:c>
+      <x:c r="Q302" t="str">
+        <x:v>In progress</x:v>
+      </x:c>
     </x:row>
     <x:row r="303">
-      <x:c r="A303"/>
-      <x:c r="B303"/>
-      <x:c r="C303"/>
-      <x:c r="D303"/>
+      <x:c r="A303" t="str">
+        <x:v>PRPSTFPT103</x:v>
+      </x:c>
+      <x:c r="B303" t="str">
+        <x:v>Foc Soca Lhr</x:v>
+      </x:c>
+      <x:c r="C303" t="str">
+        <x:v>Pending From Linkage Officer</x:v>
+      </x:c>
+      <x:c r="D303" t="str">
+        <x:v>7 October 2026</x:v>
+      </x:c>
       <x:c r="E303"/>
-      <x:c r="F303"/>
-      <x:c r="G303"/>
-      <x:c r="H303"/>
-      <x:c r="I303"/>
-      <x:c r="J303"/>
-      <x:c r="K303"/>
-      <x:c r="L303"/>
-      <x:c r="M303"/>
-      <x:c r="N303"/>
-      <x:c r="O303"/>
-      <x:c r="P303"/>
-      <x:c r="Q303"/>
+      <x:c r="F303" t="str">
+        <x:v>Lahore Campus</x:v>
+      </x:c>
+      <x:c r="G303" t="str">
+        <x:v>Faculty of Arts and Architecture</x:v>
+      </x:c>
+      <x:c r="H303" t="str">
+        <x:v>School of Creative Arts</x:v>
+      </x:c>
+      <x:c r="I303" t="str">
+        <x:v>Foc Soca Lhr</x:v>
+      </x:c>
+      <x:c r="J303" t="str"/>
+      <x:c r="K303" t="str">
+        <x:v>Seminar</x:v>
+      </x:c>
+      <x:c r="L303" t="str">
+        <x:v>Seminar / Conference / Workshop</x:v>
+      </x:c>
+      <x:c r="M303" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="N303" t="str">
+        <x:v>Industrial Option SMEDA SMEDA Small and Medium Enterprises Development Authority</x:v>
+      </x:c>
+      <x:c r="O303" t="str">
+        <x:v>Yes</x:v>
+      </x:c>
+      <x:c r="P303" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="Q303" t="str">
+        <x:v>Planned</x:v>
+      </x:c>
     </x:row>
     <x:row r="304">
-      <x:c r="A304"/>
-      <x:c r="B304"/>
-      <x:c r="C304"/>
-      <x:c r="D304"/>
-      <x:c r="E304"/>
-      <x:c r="F304"/>
-      <x:c r="G304"/>
-      <x:c r="H304"/>
-      <x:c r="I304"/>
-      <x:c r="J304"/>
-      <x:c r="K304"/>
-      <x:c r="L304"/>
-      <x:c r="M304"/>
-      <x:c r="N304"/>
-      <x:c r="O304"/>
-      <x:c r="P304"/>
-      <x:c r="Q304"/>
+      <x:c r="A304" t="str">
+        <x:v>PRPSTFPT103</x:v>
+      </x:c>
+      <x:c r="B304" t="str">
+        <x:v>Foc Soca Lhr</x:v>
+      </x:c>
+      <x:c r="C304" t="str">
+        <x:v>Pending From Linkage Officer</x:v>
+      </x:c>
+      <x:c r="D304" t="str">
+        <x:v>7 October 2026</x:v>
+      </x:c>
+      <x:c r="E304" t="str">
+        <x:v>2026-09</x:v>
+      </x:c>
+      <x:c r="F304" t="str">
+        <x:v>Lahore Campus</x:v>
+      </x:c>
+      <x:c r="G304" t="str">
+        <x:v>Faculty of Arts and Architecture</x:v>
+      </x:c>
+      <x:c r="H304" t="str">
+        <x:v>School of Creative Arts</x:v>
+      </x:c>
+      <x:c r="I304" t="str">
+        <x:v>Foc Soca Lhr</x:v>
+      </x:c>
+      <x:c r="J304" t="str"/>
+      <x:c r="K304" t="str">
+        <x:v>Industrial Visit / IV</x:v>
+      </x:c>
+      <x:c r="L304" t="str">
+        <x:v>Industrial Visit</x:v>
+      </x:c>
+      <x:c r="M304" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="N304" t="str">
+        <x:v>Alhamra Arts Council</x:v>
+      </x:c>
+      <x:c r="O304" t="str">
+        <x:v>Yes</x:v>
+      </x:c>
+      <x:c r="P304" t="str">
+        <x:v>Yes</x:v>
+      </x:c>
+      <x:c r="Q304" t="str">
+        <x:v>Completed</x:v>
+      </x:c>
     </x:row>
     <x:row r="305">
-      <x:c r="A305"/>
-      <x:c r="B305"/>
-      <x:c r="C305"/>
-      <x:c r="D305"/>
-      <x:c r="E305"/>
-      <x:c r="F305"/>
-      <x:c r="G305"/>
-      <x:c r="H305"/>
-      <x:c r="I305"/>
-      <x:c r="J305"/>
-      <x:c r="K305"/>
-      <x:c r="L305"/>
-      <x:c r="M305"/>
-      <x:c r="N305"/>
-      <x:c r="O305"/>
-      <x:c r="P305"/>
-      <x:c r="Q305"/>
+      <x:c r="A305" t="str">
+        <x:v>PRPSTFPT103</x:v>
+      </x:c>
+      <x:c r="B305" t="str">
+        <x:v>Foc Soca Lhr</x:v>
+      </x:c>
+      <x:c r="C305" t="str">
+        <x:v>Pending From Linkage Officer</x:v>
+      </x:c>
+      <x:c r="D305" t="str">
+        <x:v>7 October 2026</x:v>
+      </x:c>
+      <x:c r="E305" t="str">
+        <x:v>2026-11</x:v>
+      </x:c>
+      <x:c r="F305" t="str">
+        <x:v>Lahore Campus</x:v>
+      </x:c>
+      <x:c r="G305" t="str">
+        <x:v>Faculty of Arts and Architecture</x:v>
+      </x:c>
+      <x:c r="H305" t="str">
+        <x:v>School of Creative Arts</x:v>
+      </x:c>
+      <x:c r="I305" t="str">
+        <x:v>Foc Soca Lhr</x:v>
+      </x:c>
+      <x:c r="J305" t="str"/>
+      <x:c r="K305" t="str">
+        <x:v>Industrial Visit / IV</x:v>
+      </x:c>
+      <x:c r="L305" t="str">
+        <x:v>Industrial Visit</x:v>
+      </x:c>
+      <x:c r="M305" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="N305" t="str">
+        <x:v>Buddah Caves</x:v>
+      </x:c>
+      <x:c r="O305" t="str">
+        <x:v>Yes</x:v>
+      </x:c>
+      <x:c r="P305" t="str">
+        <x:v>Yes</x:v>
+      </x:c>
+      <x:c r="Q305" t="str">
+        <x:v>Inprogress</x:v>
+      </x:c>
     </x:row>
     <x:row r="306">
-      <x:c r="A306"/>
-      <x:c r="B306"/>
-      <x:c r="C306"/>
-      <x:c r="D306"/>
-      <x:c r="E306"/>
-      <x:c r="F306"/>
-      <x:c r="G306"/>
-      <x:c r="H306"/>
-      <x:c r="I306"/>
-      <x:c r="J306"/>
-      <x:c r="K306"/>
-      <x:c r="L306"/>
-      <x:c r="M306"/>
-      <x:c r="N306"/>
-      <x:c r="O306"/>
-      <x:c r="P306"/>
-      <x:c r="Q306"/>
+      <x:c r="A306" t="str">
+        <x:v>PRPSTFPT103</x:v>
+      </x:c>
+      <x:c r="B306" t="str">
+        <x:v>Foc Soca Lhr</x:v>
+      </x:c>
+      <x:c r="C306" t="str">
+        <x:v>Pending From Linkage Officer</x:v>
+      </x:c>
+      <x:c r="D306" t="str">
+        <x:v>7 October 2026</x:v>
+      </x:c>
+      <x:c r="E306" t="str">
+        <x:v>2026-10</x:v>
+      </x:c>
+      <x:c r="F306" t="str">
+        <x:v>Lahore Campus</x:v>
+      </x:c>
+      <x:c r="G306" t="str">
+        <x:v>Faculty of Arts and Architecture</x:v>
+      </x:c>
+      <x:c r="H306" t="str">
+        <x:v>School of Creative Arts</x:v>
+      </x:c>
+      <x:c r="I306" t="str">
+        <x:v>Foc Soca Lhr</x:v>
+      </x:c>
+      <x:c r="J306" t="str"/>
+      <x:c r="K306" t="str">
+        <x:v>Industrial Visit / IV</x:v>
+      </x:c>
+      <x:c r="L306" t="str">
+        <x:v>Industrial Visit</x:v>
+      </x:c>
+      <x:c r="M306" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="N306" t="str">
+        <x:v>OArt space</x:v>
+      </x:c>
+      <x:c r="O306" t="str">
+        <x:v>Yes</x:v>
+      </x:c>
+      <x:c r="P306" t="str">
+        <x:v>Yes</x:v>
+      </x:c>
+      <x:c r="Q306" t="str">
+        <x:v>Inprogress</x:v>
+      </x:c>
     </x:row>
     <x:row r="307">
-      <x:c r="A307"/>
-      <x:c r="B307"/>
-      <x:c r="C307"/>
-      <x:c r="D307"/>
-      <x:c r="E307"/>
-      <x:c r="F307"/>
-      <x:c r="G307"/>
-      <x:c r="H307"/>
-      <x:c r="I307"/>
-      <x:c r="J307"/>
-      <x:c r="K307"/>
-      <x:c r="L307"/>
-      <x:c r="M307"/>
-      <x:c r="N307"/>
-      <x:c r="O307"/>
-      <x:c r="P307"/>
-      <x:c r="Q307"/>
+      <x:c r="A307" t="str">
+        <x:v>PRPSTFPT103</x:v>
+      </x:c>
+      <x:c r="B307" t="str">
+        <x:v>Foc Soca Lhr</x:v>
+      </x:c>
+      <x:c r="C307" t="str">
+        <x:v>Pending From Linkage Officer</x:v>
+      </x:c>
+      <x:c r="D307" t="str">
+        <x:v>7 October 2026</x:v>
+      </x:c>
+      <x:c r="E307" t="str">
+        <x:v>2026-11</x:v>
+      </x:c>
+      <x:c r="F307" t="str">
+        <x:v>Lahore Campus</x:v>
+      </x:c>
+      <x:c r="G307" t="str">
+        <x:v>Faculty of Arts and Architecture</x:v>
+      </x:c>
+      <x:c r="H307" t="str">
+        <x:v>School of Creative Arts</x:v>
+      </x:c>
+      <x:c r="I307" t="str">
+        <x:v>Foc Soca Lhr</x:v>
+      </x:c>
+      <x:c r="J307" t="str"/>
+      <x:c r="K307" t="str">
+        <x:v>Industrial Visit / IV</x:v>
+      </x:c>
+      <x:c r="L307" t="str">
+        <x:v>Industrial Visit</x:v>
+      </x:c>
+      <x:c r="M307" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="N307" t="str">
+        <x:v>Cobalt gallery</x:v>
+      </x:c>
+      <x:c r="O307" t="str">
+        <x:v>Yes</x:v>
+      </x:c>
+      <x:c r="P307" t="str">
+        <x:v>Yes</x:v>
+      </x:c>
+      <x:c r="Q307" t="str">
+        <x:v>planned</x:v>
+      </x:c>
     </x:row>
     <x:row r="308">
-      <x:c r="A308"/>
-      <x:c r="B308"/>
-      <x:c r="C308"/>
-      <x:c r="D308"/>
+      <x:c r="A308" t="str">
+        <x:v>PRPSTFPT103</x:v>
+      </x:c>
+      <x:c r="B308" t="str">
+        <x:v>Foc Soca Lhr</x:v>
+      </x:c>
+      <x:c r="C308" t="str">
+        <x:v>Pending From Linkage Officer</x:v>
+      </x:c>
+      <x:c r="D308" t="str">
+        <x:v>7 October 2026</x:v>
+      </x:c>
       <x:c r="E308"/>
-      <x:c r="F308"/>
-      <x:c r="G308"/>
-      <x:c r="H308"/>
-      <x:c r="I308"/>
-      <x:c r="J308"/>
-      <x:c r="K308"/>
-      <x:c r="L308"/>
-      <x:c r="M308"/>
-      <x:c r="N308"/>
-      <x:c r="O308"/>
-      <x:c r="P308"/>
-      <x:c r="Q308"/>
+      <x:c r="F308" t="str">
+        <x:v>Lahore Campus</x:v>
+      </x:c>
+      <x:c r="G308" t="str">
+        <x:v>Faculty of Arts and Architecture</x:v>
+      </x:c>
+      <x:c r="H308" t="str">
+        <x:v>School of Creative Arts</x:v>
+      </x:c>
+      <x:c r="I308" t="str">
+        <x:v>Foc Soca Lhr</x:v>
+      </x:c>
+      <x:c r="J308" t="str"/>
+      <x:c r="K308" t="str">
+        <x:v>Internship / Placement</x:v>
+      </x:c>
+      <x:c r="L308" t="str">
+        <x:v>Internship/Placement</x:v>
+      </x:c>
+      <x:c r="M308" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="N308" t="str">
+        <x:v>DGPR</x:v>
+      </x:c>
+      <x:c r="O308" t="str">
+        <x:v>Yes</x:v>
+      </x:c>
+      <x:c r="P308" t="str">
+        <x:v>Yes</x:v>
+      </x:c>
+      <x:c r="Q308" t="str">
+        <x:v>Senior Students</x:v>
+      </x:c>
     </x:row>
     <x:row r="309">
-      <x:c r="A309"/>
-      <x:c r="B309"/>
-      <x:c r="C309"/>
-      <x:c r="D309"/>
+      <x:c r="A309" t="str">
+        <x:v>PRPSTFPT103</x:v>
+      </x:c>
+      <x:c r="B309" t="str">
+        <x:v>Foc Soca Lhr</x:v>
+      </x:c>
+      <x:c r="C309" t="str">
+        <x:v>Pending From Linkage Officer</x:v>
+      </x:c>
+      <x:c r="D309" t="str">
+        <x:v>7 October 2026</x:v>
+      </x:c>
       <x:c r="E309"/>
-      <x:c r="F309"/>
-      <x:c r="G309"/>
-      <x:c r="H309"/>
-      <x:c r="I309"/>
-      <x:c r="J309"/>
-      <x:c r="K309"/>
-      <x:c r="L309"/>
-      <x:c r="M309"/>
-      <x:c r="N309"/>
-      <x:c r="O309"/>
-      <x:c r="P309"/>
-      <x:c r="Q309"/>
+      <x:c r="F309" t="str">
+        <x:v>Lahore Campus</x:v>
+      </x:c>
+      <x:c r="G309" t="str">
+        <x:v>Faculty of Arts and Architecture</x:v>
+      </x:c>
+      <x:c r="H309" t="str">
+        <x:v>School of Creative Arts</x:v>
+      </x:c>
+      <x:c r="I309" t="str">
+        <x:v>Foc Soca Lhr</x:v>
+      </x:c>
+      <x:c r="J309" t="str"/>
+      <x:c r="K309" t="str">
+        <x:v>Internship / Placement</x:v>
+      </x:c>
+      <x:c r="L309" t="str">
+        <x:v>Internship/Placement</x:v>
+      </x:c>
+      <x:c r="M309" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="N309" t="str">
+        <x:v>New Channels</x:v>
+      </x:c>
+      <x:c r="O309" t="str">
+        <x:v>Yes</x:v>
+      </x:c>
+      <x:c r="P309" t="str">
+        <x:v>Yes</x:v>
+      </x:c>
+      <x:c r="Q309" t="str">
+        <x:v>Senior Students + Junior Students</x:v>
+      </x:c>
     </x:row>
     <x:row r="310">
-      <x:c r="A310"/>
-      <x:c r="B310"/>
-      <x:c r="C310"/>
-      <x:c r="D310"/>
+      <x:c r="A310" t="str">
+        <x:v>PRPSTFPT103</x:v>
+      </x:c>
+      <x:c r="B310" t="str">
+        <x:v>Foc Soca Lhr</x:v>
+      </x:c>
+      <x:c r="C310" t="str">
+        <x:v>Pending From Linkage Officer</x:v>
+      </x:c>
+      <x:c r="D310" t="str">
+        <x:v>7 October 2026</x:v>
+      </x:c>
       <x:c r="E310"/>
-      <x:c r="F310"/>
-      <x:c r="G310"/>
-      <x:c r="H310"/>
-      <x:c r="I310"/>
-      <x:c r="J310"/>
-      <x:c r="K310"/>
-      <x:c r="L310"/>
-      <x:c r="M310"/>
-      <x:c r="N310"/>
-      <x:c r="O310"/>
-      <x:c r="P310"/>
-      <x:c r="Q310"/>
+      <x:c r="F310" t="str">
+        <x:v>Lahore Campus</x:v>
+      </x:c>
+      <x:c r="G310" t="str">
+        <x:v>Faculty of Arts and Architecture</x:v>
+      </x:c>
+      <x:c r="H310" t="str">
+        <x:v>School of Creative Arts</x:v>
+      </x:c>
+      <x:c r="I310" t="str">
+        <x:v>Foc Soca Lhr</x:v>
+      </x:c>
+      <x:c r="J310" t="str"/>
+      <x:c r="K310" t="str">
+        <x:v>Guest Lecture / GLIT</x:v>
+      </x:c>
+      <x:c r="L310" t="str">
+        <x:v>Guest Lecture</x:v>
+      </x:c>
+      <x:c r="M310" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="N310" t="str">
+        <x:v>Journalist  Prominent Channels</x:v>
+      </x:c>
+      <x:c r="O310" t="str">
+        <x:v>Yes</x:v>
+      </x:c>
+      <x:c r="P310" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="Q310" t="str">
+        <x:v>Cover critical Issues of society Peace Journalism Ethical reporting Spring  Future journalism</x:v>
+      </x:c>
     </x:row>
     <x:row r="311">
-      <x:c r="A311"/>
-      <x:c r="B311"/>
-      <x:c r="C311"/>
-      <x:c r="D311"/>
+      <x:c r="A311" t="str">
+        <x:v>PRPSTFPT103</x:v>
+      </x:c>
+      <x:c r="B311" t="str">
+        <x:v>Foc Soca Lhr</x:v>
+      </x:c>
+      <x:c r="C311" t="str">
+        <x:v>Pending From Linkage Officer</x:v>
+      </x:c>
+      <x:c r="D311" t="str">
+        <x:v>7 October 2026</x:v>
+      </x:c>
       <x:c r="E311"/>
-      <x:c r="F311"/>
-      <x:c r="G311"/>
-      <x:c r="H311"/>
-      <x:c r="I311"/>
-      <x:c r="J311"/>
-      <x:c r="K311"/>
-      <x:c r="L311"/>
-      <x:c r="M311"/>
-      <x:c r="N311"/>
-      <x:c r="O311"/>
-      <x:c r="P311"/>
-      <x:c r="Q311"/>
+      <x:c r="F311" t="str">
+        <x:v>Lahore Campus</x:v>
+      </x:c>
+      <x:c r="G311" t="str">
+        <x:v>Faculty of Arts and Architecture</x:v>
+      </x:c>
+      <x:c r="H311" t="str">
+        <x:v>School of Creative Arts</x:v>
+      </x:c>
+      <x:c r="I311" t="str">
+        <x:v>Foc Soca Lhr</x:v>
+      </x:c>
+      <x:c r="J311" t="str"/>
+      <x:c r="K311" t="str">
+        <x:v>Guest Lecture / GLIT</x:v>
+      </x:c>
+      <x:c r="L311" t="str">
+        <x:v>Guest Lecture</x:v>
+      </x:c>
+      <x:c r="M311" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="N311" t="str">
+        <x:v>IAB Meeting  Industry Consultation</x:v>
+      </x:c>
+      <x:c r="O311" t="str">
+        <x:v>Yes</x:v>
+      </x:c>
+      <x:c r="P311" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="Q311" t="str">
+        <x:v>Planned</x:v>
+      </x:c>
     </x:row>
     <x:row r="312">
-      <x:c r="A312"/>
-      <x:c r="B312"/>
-      <x:c r="C312"/>
-      <x:c r="D312"/>
-      <x:c r="E312"/>
-      <x:c r="F312"/>
-      <x:c r="G312"/>
-      <x:c r="H312"/>
-      <x:c r="I312"/>
-      <x:c r="J312"/>
-      <x:c r="K312"/>
-      <x:c r="L312"/>
-      <x:c r="M312"/>
-      <x:c r="N312"/>
-      <x:c r="O312"/>
-      <x:c r="P312"/>
-      <x:c r="Q312"/>
+      <x:c r="A312" t="str">
+        <x:v>PRPSTFPT103</x:v>
+      </x:c>
+      <x:c r="B312" t="str">
+        <x:v>Foc Soca Lhr</x:v>
+      </x:c>
+      <x:c r="C312" t="str">
+        <x:v>Pending From Linkage Officer</x:v>
+      </x:c>
+      <x:c r="D312" t="str">
+        <x:v>7 October 2026</x:v>
+      </x:c>
+      <x:c r="E312" t="str">
+        <x:v>2026-12</x:v>
+      </x:c>
+      <x:c r="F312" t="str">
+        <x:v>Lahore Campus</x:v>
+      </x:c>
+      <x:c r="G312" t="str">
+        <x:v>Faculty of Arts and Architecture</x:v>
+      </x:c>
+      <x:c r="H312" t="str">
+        <x:v>School of Creative Arts</x:v>
+      </x:c>
+      <x:c r="I312" t="str">
+        <x:v>Foc Soca Lhr</x:v>
+      </x:c>
+      <x:c r="J312" t="str"/>
+      <x:c r="K312" t="str">
+        <x:v>Others</x:v>
+      </x:c>
+      <x:c r="L312" t="str">
+        <x:v>Others</x:v>
+      </x:c>
+      <x:c r="M312" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="N312" t="str">
+        <x:v>Lahore Safe City Blood Bank</x:v>
+      </x:c>
+      <x:c r="O312" t="str">
+        <x:v>Yes</x:v>
+      </x:c>
+      <x:c r="P312" t="str">
+        <x:v>Yes</x:v>
+      </x:c>
+      <x:c r="Q312" t="str">
+        <x:v>Blood Donation  Awareness Campaign</x:v>
+      </x:c>
     </x:row>
     <x:row r="313">
-      <x:c r="A313"/>
-      <x:c r="B313"/>
-      <x:c r="C313"/>
-      <x:c r="D313"/>
-      <x:c r="E313"/>
-      <x:c r="F313"/>
-      <x:c r="G313"/>
-      <x:c r="H313"/>
-      <x:c r="I313"/>
-      <x:c r="J313"/>
-      <x:c r="K313"/>
-      <x:c r="L313"/>
-      <x:c r="M313"/>
-      <x:c r="N313"/>
-      <x:c r="O313"/>
-      <x:c r="P313"/>
-      <x:c r="Q313"/>
+      <x:c r="A313" t="str">
+        <x:v>PRPSTFPT103</x:v>
+      </x:c>
+      <x:c r="B313" t="str">
+        <x:v>Foc Soca Lhr</x:v>
+      </x:c>
+      <x:c r="C313" t="str">
+        <x:v>Pending From Linkage Officer</x:v>
+      </x:c>
+      <x:c r="D313" t="str">
+        <x:v>7 October 2026</x:v>
+      </x:c>
+      <x:c r="E313" t="str">
+        <x:v>2026-11</x:v>
+      </x:c>
+      <x:c r="F313" t="str">
+        <x:v>Lahore Campus</x:v>
+      </x:c>
+      <x:c r="G313" t="str">
+        <x:v>Faculty of Arts and Architecture</x:v>
+      </x:c>
+      <x:c r="H313" t="str">
+        <x:v>School of Creative Arts</x:v>
+      </x:c>
+      <x:c r="I313" t="str">
+        <x:v>Foc Soca Lhr</x:v>
+      </x:c>
+      <x:c r="J313" t="str"/>
+      <x:c r="K313" t="str">
+        <x:v>Industrial Visit / IV</x:v>
+      </x:c>
+      <x:c r="L313" t="str">
+        <x:v>Industrial Visit</x:v>
+      </x:c>
+      <x:c r="M313" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="N313" t="str">
+        <x:v>CEGA Centre of Excellence in Gaming and Animation</x:v>
+      </x:c>
+      <x:c r="O313" t="str">
+        <x:v>Yes</x:v>
+      </x:c>
+      <x:c r="P313" t="str">
+        <x:v>Yes</x:v>
+      </x:c>
+      <x:c r="Q313" t="str">
+        <x:v>Inprogress</x:v>
+      </x:c>
     </x:row>
     <x:row r="314">
-      <x:c r="A314"/>
-      <x:c r="B314"/>
-      <x:c r="C314"/>
-      <x:c r="D314"/>
-      <x:c r="E314"/>
-      <x:c r="F314"/>
-      <x:c r="G314"/>
-      <x:c r="H314"/>
-      <x:c r="I314"/>
-      <x:c r="J314"/>
-      <x:c r="K314"/>
-      <x:c r="L314"/>
-      <x:c r="M314"/>
-      <x:c r="N314"/>
-      <x:c r="O314"/>
-      <x:c r="P314"/>
-      <x:c r="Q314"/>
+      <x:c r="A314" t="str">
+        <x:v>PRPSTFPT100</x:v>
+      </x:c>
+      <x:c r="B314" t="str">
+        <x:v>Foc Siss Lhr</x:v>
+      </x:c>
+      <x:c r="C314" t="str">
+        <x:v>Pending From Linkage Officer</x:v>
+      </x:c>
+      <x:c r="D314" t="str">
+        <x:v>2 October 2026</x:v>
+      </x:c>
+      <x:c r="E314" t="str">
+        <x:v>2026-08-31</x:v>
+      </x:c>
+      <x:c r="F314" t="str">
+        <x:v>Lahore Campus</x:v>
+      </x:c>
+      <x:c r="G314" t="str">
+        <x:v>Faculty of Social Sciences</x:v>
+      </x:c>
+      <x:c r="H314" t="str">
+        <x:v>School of Integrated Social Science</x:v>
+      </x:c>
+      <x:c r="I314" t="str">
+        <x:v>Foc Siss Lhr</x:v>
+      </x:c>
+      <x:c r="J314" t="str"/>
+      <x:c r="K314" t="str">
+        <x:v>Guest Lecture / GLIT</x:v>
+      </x:c>
+      <x:c r="L314" t="str">
+        <x:v>GLIT</x:v>
+      </x:c>
+      <x:c r="M314" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="N314" t="str">
+        <x:v>T</x:v>
+      </x:c>
+      <x:c r="O314" t="str">
+        <x:v>Yes</x:v>
+      </x:c>
+      <x:c r="P314" t="str">
+        <x:v>Yes</x:v>
+      </x:c>
+      <x:c r="Q314" t="str"/>
     </x:row>
     <x:row r="315">
-      <x:c r="A315"/>
-      <x:c r="B315"/>
-      <x:c r="C315"/>
-      <x:c r="D315"/>
-      <x:c r="E315"/>
-      <x:c r="F315"/>
-      <x:c r="G315"/>
-      <x:c r="H315"/>
-      <x:c r="I315"/>
-      <x:c r="J315"/>
-      <x:c r="K315"/>
-      <x:c r="L315"/>
-      <x:c r="M315"/>
-      <x:c r="N315"/>
-      <x:c r="O315"/>
-      <x:c r="P315"/>
-      <x:c r="Q315"/>
+      <x:c r="A315" t="str">
+        <x:v>PRPSTFPT96</x:v>
+      </x:c>
+      <x:c r="B315" t="str">
+        <x:v>Foc Soa Lhr</x:v>
+      </x:c>
+      <x:c r="C315" t="str">
+        <x:v>Pending From Linkage Officer</x:v>
+      </x:c>
+      <x:c r="D315" t="str">
+        <x:v>1 October 2026</x:v>
+      </x:c>
+      <x:c r="E315" t="str">
+        <x:v>2026-09</x:v>
+      </x:c>
+      <x:c r="F315" t="str">
+        <x:v>Lahore Campus</x:v>
+      </x:c>
+      <x:c r="G315" t="str">
+        <x:v>Faculty of Arts and Architecture</x:v>
+      </x:c>
+      <x:c r="H315" t="str">
+        <x:v>School of Architecture</x:v>
+      </x:c>
+      <x:c r="I315" t="str">
+        <x:v>Foc Soa Lhr</x:v>
+      </x:c>
+      <x:c r="J315" t="str"/>
+      <x:c r="K315" t="str">
+        <x:v>Seminar</x:v>
+      </x:c>
+      <x:c r="L315" t="str">
+        <x:v>Seminar / Conference / Workshop</x:v>
+      </x:c>
+      <x:c r="M315" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="N315" t="str">
+        <x:v>Institute of Architects of Pakistan IAP</x:v>
+      </x:c>
+      <x:c r="O315" t="str">
+        <x:v>Yes</x:v>
+      </x:c>
+      <x:c r="P315" t="str">
+        <x:v>Yes</x:v>
+      </x:c>
+      <x:c r="Q315" t="str">
+        <x:v>A day of ideas, conversations, and new possibilities around AI and the future of architecture in Pakistan.  From thought-provoking discussions to meaningful exchanges, “AI &amp; The Future of Architecture in Pakistan” brought together architects, educators, students, and design thinkers to explore how technology is reshaping the way we imagine and create our built environment.</x:v>
+      </x:c>
     </x:row>
     <x:row r="316">
-      <x:c r="A316"/>
-      <x:c r="B316"/>
-      <x:c r="C316"/>
-      <x:c r="D316"/>
-      <x:c r="E316"/>
-      <x:c r="F316"/>
-      <x:c r="G316"/>
-      <x:c r="H316"/>
-      <x:c r="I316"/>
-      <x:c r="J316"/>
-      <x:c r="K316"/>
-      <x:c r="L316"/>
-      <x:c r="M316"/>
-      <x:c r="N316"/>
-      <x:c r="O316"/>
-      <x:c r="P316"/>
-      <x:c r="Q316"/>
+      <x:c r="A316" t="str">
+        <x:v>PRPSTFPT74</x:v>
+      </x:c>
+      <x:c r="B316" t="str">
+        <x:v>Foc Uifsrt Lhr</x:v>
+      </x:c>
+      <x:c r="C316" t="str">
+        <x:v>Pending From Linkage Officer</x:v>
+      </x:c>
+      <x:c r="D316" t="str">
+        <x:v>31 July 2026</x:v>
+      </x:c>
+      <x:c r="E316" t="str">
+        <x:v>2026-04</x:v>
+      </x:c>
+      <x:c r="F316" t="str">
+        <x:v>Lahore Campus</x:v>
+      </x:c>
+      <x:c r="G316" t="str">
+        <x:v>Faculty of Allied Health Sciences</x:v>
+      </x:c>
+      <x:c r="H316" t="str">
+        <x:v>University Institute of Food Science &amp; Technology</x:v>
+      </x:c>
+      <x:c r="I316" t="str">
+        <x:v>Foc Uifsrt Lhr</x:v>
+      </x:c>
+      <x:c r="J316" t="str"/>
+      <x:c r="K316" t="str">
+        <x:v>Industrial Visit / IV</x:v>
+      </x:c>
+      <x:c r="L316" t="str">
+        <x:v>IV</x:v>
+      </x:c>
+      <x:c r="M316" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="N316" t="str">
+        <x:v>Post Harvest Research Center, AARI</x:v>
+      </x:c>
+      <x:c r="O316" t="str">
+        <x:v>Yes</x:v>
+      </x:c>
+      <x:c r="P316" t="str">
+        <x:v>Yes</x:v>
+      </x:c>
+      <x:c r="Q316" t="str">
+        <x:v>Visited and gain practical knowledge</x:v>
+      </x:c>
     </x:row>
     <x:row r="317">
-      <x:c r="A317"/>
-      <x:c r="B317"/>
-      <x:c r="C317"/>
-      <x:c r="D317"/>
-      <x:c r="E317"/>
-      <x:c r="F317"/>
-      <x:c r="G317"/>
-      <x:c r="H317"/>
-      <x:c r="I317"/>
-      <x:c r="J317"/>
-      <x:c r="K317"/>
-      <x:c r="L317"/>
-      <x:c r="M317"/>
-      <x:c r="N317"/>
-      <x:c r="O317"/>
-      <x:c r="P317"/>
-      <x:c r="Q317"/>
+      <x:c r="A317" t="str">
+        <x:v>PRPSTFPT74</x:v>
+      </x:c>
+      <x:c r="B317" t="str">
+        <x:v>Foc Uifsrt Lhr</x:v>
+      </x:c>
+      <x:c r="C317" t="str">
+        <x:v>Pending From Linkage Officer</x:v>
+      </x:c>
+      <x:c r="D317" t="str">
+        <x:v>31 July 2026</x:v>
+      </x:c>
+      <x:c r="E317" t="str">
+        <x:v>2026-04</x:v>
+      </x:c>
+      <x:c r="F317" t="str">
+        <x:v>Lahore Campus</x:v>
+      </x:c>
+      <x:c r="G317" t="str">
+        <x:v>Faculty of Allied Health Sciences</x:v>
+      </x:c>
+      <x:c r="H317" t="str">
+        <x:v>University Institute of Food Science &amp; Technology</x:v>
+      </x:c>
+      <x:c r="I317" t="str">
+        <x:v>Foc Uifsrt Lhr</x:v>
+      </x:c>
+      <x:c r="J317" t="str"/>
+      <x:c r="K317" t="str">
+        <x:v>Industrial Visit / IV</x:v>
+      </x:c>
+      <x:c r="L317" t="str">
+        <x:v>IV</x:v>
+      </x:c>
+      <x:c r="M317" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="N317" t="str">
+        <x:v>Pak Korea Nutrition Center, PKNC, Faisalabad</x:v>
+      </x:c>
+      <x:c r="O317" t="str">
+        <x:v>Yes</x:v>
+      </x:c>
+      <x:c r="P317" t="str">
+        <x:v>Yes</x:v>
+      </x:c>
+      <x:c r="Q317" t="str">
+        <x:v>Look into research opportunities</x:v>
+      </x:c>
     </x:row>
     <x:row r="318">
-      <x:c r="A318"/>
-      <x:c r="B318"/>
-      <x:c r="C318"/>
-      <x:c r="D318"/>
-      <x:c r="E318"/>
-      <x:c r="F318"/>
-      <x:c r="G318"/>
-      <x:c r="H318"/>
-      <x:c r="I318"/>
-      <x:c r="J318"/>
-      <x:c r="K318"/>
-      <x:c r="L318"/>
-      <x:c r="M318"/>
-      <x:c r="N318"/>
-      <x:c r="O318"/>
-      <x:c r="P318"/>
-      <x:c r="Q318"/>
+      <x:c r="A318" t="str">
+        <x:v>PRPSTFPT74</x:v>
+      </x:c>
+      <x:c r="B318" t="str">
+        <x:v>Foc Uifsrt Lhr</x:v>
+      </x:c>
+      <x:c r="C318" t="str">
+        <x:v>Pending From Linkage Officer</x:v>
+      </x:c>
+      <x:c r="D318" t="str">
+        <x:v>31 July 2026</x:v>
+      </x:c>
+      <x:c r="E318" t="str">
+        <x:v>2026-04</x:v>
+      </x:c>
+      <x:c r="F318" t="str">
+        <x:v>Lahore Campus</x:v>
+      </x:c>
+      <x:c r="G318" t="str">
+        <x:v>Faculty of Allied Health Sciences</x:v>
+      </x:c>
+      <x:c r="H318" t="str">
+        <x:v>University Institute of Food Science &amp; Technology</x:v>
+      </x:c>
+      <x:c r="I318" t="str">
+        <x:v>Foc Uifsrt Lhr</x:v>
+      </x:c>
+      <x:c r="J318" t="str"/>
+      <x:c r="K318" t="str">
+        <x:v>Research Collaboration</x:v>
+      </x:c>
+      <x:c r="L318" t="str">
+        <x:v>Research Collaboration</x:v>
+      </x:c>
+      <x:c r="M318" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="N318" t="str">
+        <x:v>Punjab Agriculture &amp; Meat Company (PAMCO)</x:v>
+      </x:c>
+      <x:c r="O318" t="str">
+        <x:v>Yes</x:v>
+      </x:c>
+      <x:c r="P318" t="str">
+        <x:v>Yes</x:v>
+      </x:c>
+      <x:c r="Q318" t="str">
+        <x:v>Gained Practical Knowledge</x:v>
+      </x:c>
     </x:row>
     <x:row r="319">
-      <x:c r="A319"/>
-      <x:c r="B319"/>
-      <x:c r="C319"/>
-      <x:c r="D319"/>
-      <x:c r="E319"/>
-      <x:c r="F319"/>
-      <x:c r="G319"/>
-      <x:c r="H319"/>
-      <x:c r="I319"/>
-      <x:c r="J319"/>
-      <x:c r="K319"/>
-      <x:c r="L319"/>
-      <x:c r="M319"/>
-      <x:c r="N319"/>
-      <x:c r="O319"/>
-      <x:c r="P319"/>
-      <x:c r="Q319"/>
+      <x:c r="A319" t="str">
+        <x:v>PRPSTFPT74</x:v>
+      </x:c>
+      <x:c r="B319" t="str">
+        <x:v>Foc Uifsrt Lhr</x:v>
+      </x:c>
+      <x:c r="C319" t="str">
+        <x:v>Pending From Linkage Officer</x:v>
+      </x:c>
+      <x:c r="D319" t="str">
+        <x:v>31 July 2026</x:v>
+      </x:c>
+      <x:c r="E319" t="str">
+        <x:v>2026-05</x:v>
+      </x:c>
+      <x:c r="F319" t="str">
+        <x:v>Lahore Campus</x:v>
+      </x:c>
+      <x:c r="G319" t="str">
+        <x:v>Faculty of Allied Health Sciences</x:v>
+      </x:c>
+      <x:c r="H319" t="str">
+        <x:v>University Institute of Food Science &amp; Technology</x:v>
+      </x:c>
+      <x:c r="I319" t="str">
+        <x:v>Foc Uifsrt Lhr</x:v>
+      </x:c>
+      <x:c r="J319" t="str"/>
+      <x:c r="K319" t="str">
+        <x:v>Industrial Visit / IV</x:v>
+      </x:c>
+      <x:c r="L319" t="str">
+        <x:v>IV</x:v>
+      </x:c>
+      <x:c r="M319" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="N319" t="str">
+        <x:v>Bonjour Reliance Foods, Lahore</x:v>
+      </x:c>
+      <x:c r="O319" t="str">
+        <x:v>Yes</x:v>
+      </x:c>
+      <x:c r="P319" t="str">
+        <x:v>Yes</x:v>
+      </x:c>
+      <x:c r="Q319" t="str">
+        <x:v>Visited and Gained Practical Knowledge</x:v>
+      </x:c>
     </x:row>
     <x:row r="320">
-      <x:c r="A320"/>
-      <x:c r="B320"/>
-      <x:c r="C320"/>
-      <x:c r="D320"/>
-      <x:c r="E320"/>
-      <x:c r="F320"/>
-      <x:c r="G320"/>
-      <x:c r="H320"/>
-      <x:c r="I320"/>
-      <x:c r="J320"/>
-      <x:c r="K320"/>
-      <x:c r="L320"/>
-      <x:c r="M320"/>
-      <x:c r="N320"/>
-      <x:c r="O320"/>
-      <x:c r="P320"/>
-      <x:c r="Q320"/>
+      <x:c r="A320" t="str">
+        <x:v>PRPSTFPT43</x:v>
+      </x:c>
+      <x:c r="B320" t="str">
+        <x:v>Foc Doim Lhr</x:v>
+      </x:c>
+      <x:c r="C320" t="str">
+        <x:v>Pending From Linkage Officer</x:v>
+      </x:c>
+      <x:c r="D320" t="str">
+        <x:v>21 July 2026</x:v>
+      </x:c>
+      <x:c r="E320" t="str">
+        <x:v>2026-05</x:v>
+      </x:c>
+      <x:c r="F320" t="str">
+        <x:v>Lahore Campus</x:v>
+      </x:c>
+      <x:c r="G320" t="str">
+        <x:v>Faculty of Management Sciences</x:v>
+      </x:c>
+      <x:c r="H320" t="str">
+        <x:v>Department of Information Management</x:v>
+      </x:c>
+      <x:c r="I320" t="str">
+        <x:v>Foc Doim Lhr</x:v>
+      </x:c>
+      <x:c r="J320" t="str"/>
+      <x:c r="K320" t="str">
+        <x:v>Guest Lecture / GLIT</x:v>
+      </x:c>
+      <x:c r="L320" t="str">
+        <x:v>GLIT</x:v>
+      </x:c>
+      <x:c r="M320" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="N320" t="str">
+        <x:v>UOL</x:v>
+      </x:c>
+      <x:c r="O320" t="str">
+        <x:v>Yes</x:v>
+      </x:c>
+      <x:c r="P320" t="str">
+        <x:v>Yes</x:v>
+      </x:c>
+      <x:c r="Q320" t="str">
+        <x:v>Mr Tahir Fareed delivered a lecture on research techniques. Activity Concluded.</x:v>
+      </x:c>
     </x:row>
     <x:row r="321">
-      <x:c r="A321"/>
-      <x:c r="B321"/>
-      <x:c r="C321"/>
-      <x:c r="D321"/>
-      <x:c r="E321"/>
-      <x:c r="F321"/>
-      <x:c r="G321"/>
-      <x:c r="H321"/>
-      <x:c r="I321"/>
-      <x:c r="J321"/>
-      <x:c r="K321"/>
-      <x:c r="L321"/>
-      <x:c r="M321"/>
-      <x:c r="N321"/>
-      <x:c r="O321"/>
-      <x:c r="P321"/>
-      <x:c r="Q321"/>
+      <x:c r="A321" t="str">
+        <x:v>PRPSTFPT43</x:v>
+      </x:c>
+      <x:c r="B321" t="str">
+        <x:v>Foc Doim Lhr</x:v>
+      </x:c>
+      <x:c r="C321" t="str">
+        <x:v>Pending From Linkage Officer</x:v>
+      </x:c>
+      <x:c r="D321" t="str">
+        <x:v>21 July 2026</x:v>
+      </x:c>
+      <x:c r="E321" t="str">
+        <x:v>2026-05</x:v>
+      </x:c>
+      <x:c r="F321" t="str">
+        <x:v>Lahore Campus</x:v>
+      </x:c>
+      <x:c r="G321" t="str">
+        <x:v>Faculty of Management Sciences</x:v>
+      </x:c>
+      <x:c r="H321" t="str">
+        <x:v>Department of Information Management</x:v>
+      </x:c>
+      <x:c r="I321" t="str">
+        <x:v>Foc Doim Lhr</x:v>
+      </x:c>
+      <x:c r="J321" t="str"/>
+      <x:c r="K321" t="str">
+        <x:v>Guest Lecture / GLIT</x:v>
+      </x:c>
+      <x:c r="L321" t="str">
+        <x:v>GLIT</x:v>
+      </x:c>
+      <x:c r="M321" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="N321" t="str">
+        <x:v>UOL</x:v>
+      </x:c>
+      <x:c r="O321" t="str">
+        <x:v>Yes</x:v>
+      </x:c>
+      <x:c r="P321" t="str">
+        <x:v>Yes</x:v>
+      </x:c>
+      <x:c r="Q321" t="str">
+        <x:v>Ms Rimsha Qayyum delivered a lectur on Qualitative Research Methods. Activity Concluded.</x:v>
+      </x:c>
     </x:row>
     <x:row r="322">
-      <x:c r="A322"/>
-      <x:c r="B322"/>
-      <x:c r="C322"/>
-      <x:c r="D322"/>
-      <x:c r="E322"/>
-      <x:c r="F322"/>
-      <x:c r="G322"/>
-      <x:c r="H322"/>
-      <x:c r="I322"/>
-      <x:c r="J322"/>
-      <x:c r="K322"/>
-      <x:c r="L322"/>
-      <x:c r="M322"/>
-      <x:c r="N322"/>
-      <x:c r="O322"/>
-      <x:c r="P322"/>
-      <x:c r="Q322"/>
+      <x:c r="A322" t="str">
+        <x:v>PRPSTFPT43</x:v>
+      </x:c>
+      <x:c r="B322" t="str">
+        <x:v>Foc Doim Lhr</x:v>
+      </x:c>
+      <x:c r="C322" t="str">
+        <x:v>Pending From Linkage Officer</x:v>
+      </x:c>
+      <x:c r="D322" t="str">
+        <x:v>21 July 2026</x:v>
+      </x:c>
+      <x:c r="E322" t="str">
+        <x:v>2026-06</x:v>
+      </x:c>
+      <x:c r="F322" t="str">
+        <x:v>Lahore Campus</x:v>
+      </x:c>
+      <x:c r="G322" t="str">
+        <x:v>Faculty of Management Sciences</x:v>
+      </x:c>
+      <x:c r="H322" t="str">
+        <x:v>Department of Information Management</x:v>
+      </x:c>
+      <x:c r="I322" t="str">
+        <x:v>Foc Doim Lhr</x:v>
+      </x:c>
+      <x:c r="J322" t="str"/>
+      <x:c r="K322" t="str">
+        <x:v>Seminar</x:v>
+      </x:c>
+      <x:c r="L322" t="str">
+        <x:v>Seminar / Conference / Workshop</x:v>
+      </x:c>
+      <x:c r="M322" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="N322" t="str">
+        <x:v>UK</x:v>
+      </x:c>
+      <x:c r="O322" t="str">
+        <x:v>Yes</x:v>
+      </x:c>
+      <x:c r="P322" t="str">
+        <x:v>Yes</x:v>
+      </x:c>
+      <x:c r="Q322" t="str">
+        <x:v>International Webinar Series 2026; Writing Literature Review Ethically in the Age of AI (Resource Person Yanhua Liu) UK, The webinar aimed to enhance participants’ understanding of effective literature review practices, ethical academic writing, and the responsible use of Artificial Intelligence (AI) in research. Activity Concluded.</x:v>
+      </x:c>
     </x:row>
     <x:row r="323">
-      <x:c r="A323"/>
-      <x:c r="B323"/>
-      <x:c r="C323"/>
-      <x:c r="D323"/>
-      <x:c r="E323"/>
-      <x:c r="F323"/>
-      <x:c r="G323"/>
-      <x:c r="H323"/>
-      <x:c r="I323"/>
-      <x:c r="J323"/>
-      <x:c r="K323"/>
-      <x:c r="L323"/>
-      <x:c r="M323"/>
-      <x:c r="N323"/>
-      <x:c r="O323"/>
-      <x:c r="P323"/>
-      <x:c r="Q323"/>
+      <x:c r="A323" t="str">
+        <x:v>PRPSTFPT43</x:v>
+      </x:c>
+      <x:c r="B323" t="str">
+        <x:v>Foc Doim Lhr</x:v>
+      </x:c>
+      <x:c r="C323" t="str">
+        <x:v>Pending From Linkage Officer</x:v>
+      </x:c>
+      <x:c r="D323" t="str">
+        <x:v>21 July 2026</x:v>
+      </x:c>
+      <x:c r="E323" t="str">
+        <x:v>2026-06</x:v>
+      </x:c>
+      <x:c r="F323" t="str">
+        <x:v>Lahore Campus</x:v>
+      </x:c>
+      <x:c r="G323" t="str">
+        <x:v>Faculty of Management Sciences</x:v>
+      </x:c>
+      <x:c r="H323" t="str">
+        <x:v>Department of Information Management</x:v>
+      </x:c>
+      <x:c r="I323" t="str">
+        <x:v>Foc Doim Lhr</x:v>
+      </x:c>
+      <x:c r="J323" t="str"/>
+      <x:c r="K323" t="str">
+        <x:v>Others</x:v>
+      </x:c>
+      <x:c r="L323" t="str">
+        <x:v>Others</x:v>
+      </x:c>
+      <x:c r="M323" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="N323" t="str">
+        <x:v>Department of Information Management (DoIM) UOL</x:v>
+      </x:c>
+      <x:c r="O323" t="str">
+        <x:v>Yes</x:v>
+      </x:c>
+      <x:c r="P323" t="str">
+        <x:v>Yes</x:v>
+      </x:c>
+      <x:c r="Q323" t="str">
+        <x:v>Student Poster Exhibition and Competition 2026 at The Department of Information Management &amp; Completion of Batch Spring 2026 First Semester, and 2nd Semester by Batch Fall 2025. To promoted research culture and academic creativity among students  and	strengthened research communication and poster presentation skills. Activity Concluded.</x:v>
+      </x:c>
     </x:row>
     <x:row r="324">
-      <x:c r="A324"/>
-      <x:c r="B324"/>
-      <x:c r="C324"/>
-      <x:c r="D324"/>
-      <x:c r="E324"/>
-      <x:c r="F324"/>
-      <x:c r="G324"/>
-      <x:c r="H324"/>
-      <x:c r="I324"/>
-      <x:c r="J324"/>
-      <x:c r="K324"/>
-      <x:c r="L324"/>
-      <x:c r="M324"/>
-      <x:c r="N324"/>
-      <x:c r="O324"/>
-      <x:c r="P324"/>
-      <x:c r="Q324"/>
+      <x:c r="A324" t="str">
+        <x:v>PRPSTFPT43</x:v>
+      </x:c>
+      <x:c r="B324" t="str">
+        <x:v>Foc Doim Lhr</x:v>
+      </x:c>
+      <x:c r="C324" t="str">
+        <x:v>Pending From Linkage Officer</x:v>
+      </x:c>
+      <x:c r="D324" t="str">
+        <x:v>21 July 2026</x:v>
+      </x:c>
+      <x:c r="E324" t="str">
+        <x:v>2026-07</x:v>
+      </x:c>
+      <x:c r="F324" t="str">
+        <x:v>Lahore Campus</x:v>
+      </x:c>
+      <x:c r="G324" t="str">
+        <x:v>Faculty of Management Sciences</x:v>
+      </x:c>
+      <x:c r="H324" t="str">
+        <x:v>Department of Information Management</x:v>
+      </x:c>
+      <x:c r="I324" t="str">
+        <x:v>Foc Doim Lhr</x:v>
+      </x:c>
+      <x:c r="J324" t="str"/>
+      <x:c r="K324" t="str">
+        <x:v>Seminar</x:v>
+      </x:c>
+      <x:c r="L324" t="str">
+        <x:v>Seminar / Conference / Workshop</x:v>
+      </x:c>
+      <x:c r="M324" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="N324" t="str">
+        <x:v>Department of Information Management (DoIM) UOL</x:v>
+      </x:c>
+      <x:c r="O324" t="str">
+        <x:v>Yes</x:v>
+      </x:c>
+      <x:c r="P324" t="str">
+        <x:v>Yes</x:v>
+      </x:c>
+      <x:c r="Q324" t="str">
+        <x:v>𝐁𝐞𝐡𝐚𝐯𝐢𝐨𝐫𝐚𝐥 𝐌𝐚𝐧𝐚𝐠𝐞𝐦𝐞𝐧𝐭: 𝐓𝐡𝐞 𝐉𝐨𝐮𝐫𝐧𝐞𝐲 𝐨𝐟 𝐏𝐫𝐨𝐟𝐞𝐬𝐢𝐨𝐧𝐚𝐥 𝐄𝐱𝐜𝐞𝐥𝐞𝐧𝐜𝐞. (Resource Person Prf. Dr. Zaheer Ahmad)An excellent opportunity for library professionals to enhance the attitudes, skills, and behaviors essential for professional success. Activity Concluded.</x:v>
+      </x:c>
     </x:row>
     <x:row r="325">
-      <x:c r="A325"/>
-      <x:c r="B325"/>
-      <x:c r="C325"/>
-      <x:c r="D325"/>
-      <x:c r="E325"/>
-      <x:c r="F325"/>
-      <x:c r="G325"/>
-      <x:c r="H325"/>
-      <x:c r="I325"/>
-      <x:c r="J325"/>
-      <x:c r="K325"/>
-      <x:c r="L325"/>
-      <x:c r="M325"/>
-      <x:c r="N325"/>
-      <x:c r="O325"/>
-      <x:c r="P325"/>
-      <x:c r="Q325"/>
+      <x:c r="A325" t="str">
+        <x:v>PRPSTFPT43</x:v>
+      </x:c>
+      <x:c r="B325" t="str">
+        <x:v>Foc Doim Lhr</x:v>
+      </x:c>
+      <x:c r="C325" t="str">
+        <x:v>Pending From Linkage Officer</x:v>
+      </x:c>
+      <x:c r="D325" t="str">
+        <x:v>21 July 2026</x:v>
+      </x:c>
+      <x:c r="E325" t="str">
+        <x:v>2026-07</x:v>
+      </x:c>
+      <x:c r="F325" t="str">
+        <x:v>Lahore Campus</x:v>
+      </x:c>
+      <x:c r="G325" t="str">
+        <x:v>Faculty of Management Sciences</x:v>
+      </x:c>
+      <x:c r="H325" t="str">
+        <x:v>Department of Information Management</x:v>
+      </x:c>
+      <x:c r="I325" t="str">
+        <x:v>Foc Doim Lhr</x:v>
+      </x:c>
+      <x:c r="J325" t="str"/>
+      <x:c r="K325" t="str">
+        <x:v>Seminar</x:v>
+      </x:c>
+      <x:c r="L325" t="str">
+        <x:v>Seminar / Conference / Workshop</x:v>
+      </x:c>
+      <x:c r="M325" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="N325" t="str">
+        <x:v>COMSATS University Islamabad, Lahore Campus</x:v>
+      </x:c>
+      <x:c r="O325" t="str">
+        <x:v>Yes</x:v>
+      </x:c>
+      <x:c r="P325" t="str">
+        <x:v>Yes</x:v>
+      </x:c>
+      <x:c r="Q325" t="str">
+        <x:v>𝐆𝐥𝐨𝐛𝐚𝐥 𝐃𝐢𝐚𝐥𝐨𝐠𝐮𝐞 𝐨𝐧 𝐑𝐞𝐬𝐞𝐚𝐫𝐜𝐡 𝐁𝐞𝐲𝐨𝐧𝐝 𝐁𝐨𝐮𝐧𝐝, This academic dialogue aims to bring together researchers, faculty members, and professionals to explore emerging avenues for international research collaboration, interdisciplinary engagement, and global academic networking. Activity Concluded.𝐚𝐫𝐢𝐞𝐬: 𝐎𝐩𝐩𝐨𝐫𝐭𝐮𝐧𝐢𝐭𝐢𝐞𝐬 𝐟𝐨𝐫 𝐈𝐧𝐭𝐞𝐫𝐧𝐚𝐭𝐢𝐨𝐧𝐚𝐥 𝐂𝐨𝐥𝐥𝐚𝐛𝐨𝐫𝐚𝐭𝐢𝐨𝐧,</x:v>
+      </x:c>
     </x:row>
     <x:row r="326">
-      <x:c r="A326"/>
-      <x:c r="B326"/>
-      <x:c r="C326"/>
-      <x:c r="D326"/>
-      <x:c r="E326"/>
-      <x:c r="F326"/>
-      <x:c r="G326"/>
-      <x:c r="H326"/>
-      <x:c r="I326"/>
-      <x:c r="J326"/>
-      <x:c r="K326"/>
-      <x:c r="L326"/>
-      <x:c r="M326"/>
-      <x:c r="N326"/>
-      <x:c r="O326"/>
-      <x:c r="P326"/>
-      <x:c r="Q326"/>
+      <x:c r="A326" t="str">
+        <x:v>PRPSTFPT43</x:v>
+      </x:c>
+      <x:c r="B326" t="str">
+        <x:v>Foc Doim Lhr</x:v>
+      </x:c>
+      <x:c r="C326" t="str">
+        <x:v>Pending From Linkage Officer</x:v>
+      </x:c>
+      <x:c r="D326" t="str">
+        <x:v>21 July 2026</x:v>
+      </x:c>
+      <x:c r="E326" t="str">
+        <x:v>2026-07</x:v>
+      </x:c>
+      <x:c r="F326" t="str">
+        <x:v>Lahore Campus</x:v>
+      </x:c>
+      <x:c r="G326" t="str">
+        <x:v>Faculty of Management Sciences</x:v>
+      </x:c>
+      <x:c r="H326" t="str">
+        <x:v>Department of Information Management</x:v>
+      </x:c>
+      <x:c r="I326" t="str">
+        <x:v>Foc Doim Lhr</x:v>
+      </x:c>
+      <x:c r="J326" t="str"/>
+      <x:c r="K326" t="str">
+        <x:v>Workshop</x:v>
+      </x:c>
+      <x:c r="L326" t="str">
+        <x:v>Seminar / Conference / Workshop</x:v>
+      </x:c>
+      <x:c r="M326" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="N326" t="str">
+        <x:v>Sustainable Development Policy Institute (SDPI), Islamabad</x:v>
+      </x:c>
+      <x:c r="O326" t="str">
+        <x:v>Yes</x:v>
+      </x:c>
+      <x:c r="P326" t="str">
+        <x:v>Yes</x:v>
+      </x:c>
+      <x:c r="Q326" t="str">
+        <x:v>Synthesizing Evidence for Policy Research, during the workshop, Dr. Zaheer highlighted the importance of evidence synthesis in producing credible and policy-relevant research. He introduced systematic approaches to identifying, evaluating, and synthesizing scholarly literature, while demonstrating the responsible use of AI tools to support literature reviews and evidence-based policymaking. The session concluded with practical activities on effective literature searching, reference management, and integrating evidence into policy narratives. Participants gained valuable insights into strengthening the quality, transparency, and impact of policy research through ethical and responsible research practices.</x:v>
+      </x:c>
     </x:row>
     <x:row r="327">
-      <x:c r="A327"/>
-      <x:c r="B327"/>
-      <x:c r="C327"/>
-      <x:c r="D327"/>
-      <x:c r="E327"/>
-      <x:c r="F327"/>
-      <x:c r="G327"/>
-      <x:c r="H327"/>
-      <x:c r="I327"/>
-      <x:c r="J327"/>
-      <x:c r="K327"/>
-      <x:c r="L327"/>
-      <x:c r="M327"/>
-      <x:c r="N327"/>
-      <x:c r="O327"/>
-      <x:c r="P327"/>
-      <x:c r="Q327"/>
+      <x:c r="A327" t="str">
+        <x:v>PRPSTFPT43</x:v>
+      </x:c>
+      <x:c r="B327" t="str">
+        <x:v>Foc Doim Lhr</x:v>
+      </x:c>
+      <x:c r="C327" t="str">
+        <x:v>Pending From Linkage Officer</x:v>
+      </x:c>
+      <x:c r="D327" t="str">
+        <x:v>21 July 2026</x:v>
+      </x:c>
+      <x:c r="E327" t="str">
+        <x:v>2026-07</x:v>
+      </x:c>
+      <x:c r="F327" t="str">
+        <x:v>Lahore Campus</x:v>
+      </x:c>
+      <x:c r="G327" t="str">
+        <x:v>Faculty of Management Sciences</x:v>
+      </x:c>
+      <x:c r="H327" t="str">
+        <x:v>Department of Information Management</x:v>
+      </x:c>
+      <x:c r="I327" t="str">
+        <x:v>Foc Doim Lhr</x:v>
+      </x:c>
+      <x:c r="J327" t="str"/>
+      <x:c r="K327" t="str">
+        <x:v>Seminar</x:v>
+      </x:c>
+      <x:c r="L327" t="str">
+        <x:v>Seminar / Conference / Workshop</x:v>
+      </x:c>
+      <x:c r="M327" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="N327" t="str">
+        <x:v>The Pakistan Scientific and Technological Information Centre (PSTIC), Regional Office Lahore</x:v>
+      </x:c>
+      <x:c r="O327" t="str">
+        <x:v>Yes</x:v>
+      </x:c>
+      <x:c r="P327" t="str">
+        <x:v>Yes</x:v>
+      </x:c>
+      <x:c r="Q327" t="str">
+        <x:v>The webinar on Intelligent Literature Reviews: AI Tools, Critical Thinking, and Research Ethics,  Prof. Dr. Zaheer Ahmad, Resource Person, discussed the significance of literature reviews in identifying research gaps and building a strong scholarly foundation. He demonstrated how AI-powered tools can support literature searching, evidence synthesis, summarization, reference management, and academic writing while emphasizing that researchers must apply critical thinking, sound judgment, and ethical practices throughout the research process. He also stressed the importance of verifying AI-generated content, avoiding plagiarism and fabricated citations, and ensuring transparency in the responsible use of AI.</x:v>
+      </x:c>
     </x:row>
     <x:row r="328">
       <x:c r="A328"/>
@@ -30116,23 +31438,55 @@
       </x:c>
     </x:row>
     <x:row r="13" ht="27.600000381469727">
-      <x:c r="A13" s="2"/>
-      <x:c r="B13" s="2"/>
-      <x:c r="C13" s="2"/>
-      <x:c r="D13" s="2"/>
-      <x:c r="E13" s="2"/>
-      <x:c r="F13" s="2"/>
-      <x:c r="G13" s="2"/>
-      <x:c r="H13" s="2"/>
-      <x:c r="I13" s="2"/>
-      <x:c r="J13" s="2"/>
-      <x:c r="K13" s="2"/>
-      <x:c r="L13" s="2"/>
-      <x:c r="M13" s="2"/>
-      <x:c r="N13" s="2"/>
-      <x:c r="O13" s="2"/>
-      <x:c r="P13" s="2"/>
-      <x:c r="Q13" s="2"/>
+      <x:c r="A13" s="2" t="str">
+        <x:v>PRPSTFPT43</x:v>
+      </x:c>
+      <x:c r="B13" s="2" t="str">
+        <x:v>Foc Doim Lhr</x:v>
+      </x:c>
+      <x:c r="C13" s="2" t="str">
+        <x:v>Pending From Linkage Officer</x:v>
+      </x:c>
+      <x:c r="D13" s="2" t="str">
+        <x:v>21 July 2026</x:v>
+      </x:c>
+      <x:c r="E13" s="2" t="str">
+        <x:v>2026-07</x:v>
+      </x:c>
+      <x:c r="F13" s="2" t="str">
+        <x:v>Lahore Campus</x:v>
+      </x:c>
+      <x:c r="G13" s="2" t="str">
+        <x:v>Faculty of Management Sciences</x:v>
+      </x:c>
+      <x:c r="H13" s="2" t="str">
+        <x:v>Department of Information Management</x:v>
+      </x:c>
+      <x:c r="I13" s="2" t="str">
+        <x:v>Foc Doim Lhr</x:v>
+      </x:c>
+      <x:c r="J13" s="2" t="str"/>
+      <x:c r="K13" s="2" t="str">
+        <x:v>Workshop</x:v>
+      </x:c>
+      <x:c r="L13" s="2" t="str">
+        <x:v>Seminar / Conference / Workshop</x:v>
+      </x:c>
+      <x:c r="M13" s="2" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="N13" s="2" t="str">
+        <x:v>Sustainable Development Policy Institute (SDPI), Islamabad</x:v>
+      </x:c>
+      <x:c r="O13" s="2" t="str">
+        <x:v>Yes</x:v>
+      </x:c>
+      <x:c r="P13" s="2" t="str">
+        <x:v>Yes</x:v>
+      </x:c>
+      <x:c r="Q13" s="2" t="str">
+        <x:v>Synthesizing Evidence for Policy Research, during the workshop, Dr. Zaheer highlighted the importance of evidence synthesis in producing credible and policy-relevant research. He introduced systematic approaches to identifying, evaluating, and synthesizing scholarly literature, while demonstrating the responsible use of AI tools to support literature reviews and evidence-based policymaking. The session concluded with practical activities on effective literature searching, reference management, and integrating evidence into policy narratives. Participants gained valuable insights into strengthening the quality, transparency, and impact of policy research through ethical and responsible research practices.</x:v>
+      </x:c>
     </x:row>
     <x:row r="14" ht="27.600000381469727">
       <x:c r="A14" s="2"/>
@@ -31926,99 +33280,253 @@
       </x:c>
     </x:row>
     <x:row r="35" ht="55.20000076293945">
-      <x:c r="A35" s="15"/>
-      <x:c r="B35" s="2"/>
-      <x:c r="C35" s="2"/>
-      <x:c r="D35" s="2"/>
+      <x:c r="A35" s="15" t="str">
+        <x:v>PRPSTFPT103</x:v>
+      </x:c>
+      <x:c r="B35" s="2" t="str">
+        <x:v>Foc Soca Lhr</x:v>
+      </x:c>
+      <x:c r="C35" s="2" t="str">
+        <x:v>Pending From Linkage Officer</x:v>
+      </x:c>
+      <x:c r="D35" s="2" t="str">
+        <x:v>7 October 2026</x:v>
+      </x:c>
       <x:c r="E35" s="2"/>
-      <x:c r="F35" s="2"/>
-      <x:c r="G35" s="2"/>
-      <x:c r="H35" s="2"/>
-      <x:c r="I35" s="2"/>
-      <x:c r="J35" s="2"/>
-      <x:c r="K35" s="2"/>
-      <x:c r="L35" s="2"/>
-      <x:c r="M35" s="2"/>
-      <x:c r="N35" s="2"/>
-      <x:c r="O35" s="2"/>
-      <x:c r="P35" s="2"/>
-      <x:c r="Q35" s="16"/>
+      <x:c r="F35" s="2" t="str">
+        <x:v>Lahore Campus</x:v>
+      </x:c>
+      <x:c r="G35" s="2" t="str">
+        <x:v>Faculty of Arts and Architecture</x:v>
+      </x:c>
+      <x:c r="H35" s="2" t="str">
+        <x:v>School of Creative Arts</x:v>
+      </x:c>
+      <x:c r="I35" s="2" t="str">
+        <x:v>Foc Soca Lhr</x:v>
+      </x:c>
+      <x:c r="J35" s="2" t="str"/>
+      <x:c r="K35" s="2" t="str">
+        <x:v>Guest Lecture / GLIT</x:v>
+      </x:c>
+      <x:c r="L35" s="2" t="str">
+        <x:v>Guest Lecture</x:v>
+      </x:c>
+      <x:c r="M35" s="2" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="N35" s="2" t="str">
+        <x:v>Journalist  Prominent Channels</x:v>
+      </x:c>
+      <x:c r="O35" s="2" t="str">
+        <x:v>Yes</x:v>
+      </x:c>
+      <x:c r="P35" s="2" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="Q35" s="16" t="str">
+        <x:v>Cover critical Issues of society Peace Journalism Ethical reporting Spring  Future journalism</x:v>
+      </x:c>
     </x:row>
     <x:row r="36" ht="69">
-      <x:c r="A36" s="15"/>
-      <x:c r="B36" s="2"/>
-      <x:c r="C36" s="2"/>
-      <x:c r="D36" s="2"/>
+      <x:c r="A36" s="15" t="str">
+        <x:v>PRPSTFPT103</x:v>
+      </x:c>
+      <x:c r="B36" s="2" t="str">
+        <x:v>Foc Soca Lhr</x:v>
+      </x:c>
+      <x:c r="C36" s="2" t="str">
+        <x:v>Pending From Linkage Officer</x:v>
+      </x:c>
+      <x:c r="D36" s="2" t="str">
+        <x:v>7 October 2026</x:v>
+      </x:c>
       <x:c r="E36" s="2"/>
-      <x:c r="F36" s="2"/>
-      <x:c r="G36" s="2"/>
-      <x:c r="H36" s="2"/>
-      <x:c r="I36" s="2"/>
-      <x:c r="J36" s="2"/>
-      <x:c r="K36" s="2"/>
-      <x:c r="L36" s="2"/>
-      <x:c r="M36" s="2"/>
-      <x:c r="N36" s="2"/>
-      <x:c r="O36" s="2"/>
-      <x:c r="P36" s="2"/>
-      <x:c r="Q36" s="16"/>
+      <x:c r="F36" s="2" t="str">
+        <x:v>Lahore Campus</x:v>
+      </x:c>
+      <x:c r="G36" s="2" t="str">
+        <x:v>Faculty of Arts and Architecture</x:v>
+      </x:c>
+      <x:c r="H36" s="2" t="str">
+        <x:v>School of Creative Arts</x:v>
+      </x:c>
+      <x:c r="I36" s="2" t="str">
+        <x:v>Foc Soca Lhr</x:v>
+      </x:c>
+      <x:c r="J36" s="2" t="str"/>
+      <x:c r="K36" s="2" t="str">
+        <x:v>Guest Lecture / GLIT</x:v>
+      </x:c>
+      <x:c r="L36" s="2" t="str">
+        <x:v>Guest Lecture</x:v>
+      </x:c>
+      <x:c r="M36" s="2" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="N36" s="2" t="str">
+        <x:v>IAB Meeting  Industry Consultation</x:v>
+      </x:c>
+      <x:c r="O36" s="2" t="str">
+        <x:v>Yes</x:v>
+      </x:c>
+      <x:c r="P36" s="2" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="Q36" s="16" t="str">
+        <x:v>Planned</x:v>
+      </x:c>
     </x:row>
     <x:row r="37" ht="27.600000381469727">
-      <x:c r="A37" s="15"/>
-      <x:c r="B37" s="2"/>
-      <x:c r="C37" s="2"/>
-      <x:c r="D37" s="2"/>
-      <x:c r="E37" s="2"/>
-      <x:c r="F37" s="2"/>
-      <x:c r="G37" s="2"/>
-      <x:c r="H37" s="2"/>
-      <x:c r="I37" s="2"/>
-      <x:c r="J37" s="2"/>
-      <x:c r="K37" s="2"/>
-      <x:c r="L37" s="2"/>
-      <x:c r="M37" s="2"/>
-      <x:c r="N37" s="2"/>
-      <x:c r="O37" s="2"/>
-      <x:c r="P37" s="2"/>
-      <x:c r="Q37" s="16"/>
+      <x:c r="A37" s="15" t="str">
+        <x:v>PRPSTFPT100</x:v>
+      </x:c>
+      <x:c r="B37" s="2" t="str">
+        <x:v>Foc Siss Lhr</x:v>
+      </x:c>
+      <x:c r="C37" s="2" t="str">
+        <x:v>Pending From Linkage Officer</x:v>
+      </x:c>
+      <x:c r="D37" s="2" t="str">
+        <x:v>2 October 2026</x:v>
+      </x:c>
+      <x:c r="E37" s="2" t="str">
+        <x:v>2026-08-31</x:v>
+      </x:c>
+      <x:c r="F37" s="2" t="str">
+        <x:v>Lahore Campus</x:v>
+      </x:c>
+      <x:c r="G37" s="2" t="str">
+        <x:v>Faculty of Social Sciences</x:v>
+      </x:c>
+      <x:c r="H37" s="2" t="str">
+        <x:v>School of Integrated Social Science</x:v>
+      </x:c>
+      <x:c r="I37" s="2" t="str">
+        <x:v>Foc Siss Lhr</x:v>
+      </x:c>
+      <x:c r="J37" s="2" t="str"/>
+      <x:c r="K37" s="2" t="str">
+        <x:v>Guest Lecture / GLIT</x:v>
+      </x:c>
+      <x:c r="L37" s="2" t="str">
+        <x:v>GLIT</x:v>
+      </x:c>
+      <x:c r="M37" s="2" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="N37" s="2" t="str">
+        <x:v>T</x:v>
+      </x:c>
+      <x:c r="O37" s="2" t="str">
+        <x:v>Yes</x:v>
+      </x:c>
+      <x:c r="P37" s="2" t="str">
+        <x:v>Yes</x:v>
+      </x:c>
+      <x:c r="Q37" s="16" t="str"/>
     </x:row>
     <x:row r="38" ht="27.600000381469727">
-      <x:c r="A38" s="15"/>
-      <x:c r="B38" s="2"/>
-      <x:c r="C38" s="2"/>
-      <x:c r="D38" s="2"/>
-      <x:c r="E38" s="2"/>
-      <x:c r="F38" s="2"/>
-      <x:c r="G38" s="2"/>
-      <x:c r="H38" s="2"/>
-      <x:c r="I38" s="2"/>
-      <x:c r="J38" s="2"/>
-      <x:c r="K38" s="2"/>
-      <x:c r="L38" s="2"/>
-      <x:c r="M38" s="2"/>
-      <x:c r="N38" s="2"/>
-      <x:c r="O38" s="2"/>
-      <x:c r="P38" s="2"/>
-      <x:c r="Q38" s="16"/>
+      <x:c r="A38" s="15" t="str">
+        <x:v>PRPSTFPT43</x:v>
+      </x:c>
+      <x:c r="B38" s="2" t="str">
+        <x:v>Foc Doim Lhr</x:v>
+      </x:c>
+      <x:c r="C38" s="2" t="str">
+        <x:v>Pending From Linkage Officer</x:v>
+      </x:c>
+      <x:c r="D38" s="2" t="str">
+        <x:v>21 July 2026</x:v>
+      </x:c>
+      <x:c r="E38" s="2" t="str">
+        <x:v>2026-05</x:v>
+      </x:c>
+      <x:c r="F38" s="2" t="str">
+        <x:v>Lahore Campus</x:v>
+      </x:c>
+      <x:c r="G38" s="2" t="str">
+        <x:v>Faculty of Management Sciences</x:v>
+      </x:c>
+      <x:c r="H38" s="2" t="str">
+        <x:v>Department of Information Management</x:v>
+      </x:c>
+      <x:c r="I38" s="2" t="str">
+        <x:v>Foc Doim Lhr</x:v>
+      </x:c>
+      <x:c r="J38" s="2" t="str"/>
+      <x:c r="K38" s="2" t="str">
+        <x:v>Guest Lecture / GLIT</x:v>
+      </x:c>
+      <x:c r="L38" s="2" t="str">
+        <x:v>GLIT</x:v>
+      </x:c>
+      <x:c r="M38" s="2" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="N38" s="2" t="str">
+        <x:v>UOL</x:v>
+      </x:c>
+      <x:c r="O38" s="2" t="str">
+        <x:v>Yes</x:v>
+      </x:c>
+      <x:c r="P38" s="2" t="str">
+        <x:v>Yes</x:v>
+      </x:c>
+      <x:c r="Q38" s="16" t="str">
+        <x:v>Mr Tahir Fareed delivered a lecture on research techniques. Activity Concluded.</x:v>
+      </x:c>
     </x:row>
     <x:row r="39" ht="27.600000381469727">
-      <x:c r="A39" s="15"/>
-      <x:c r="B39" s="2"/>
-      <x:c r="C39" s="2"/>
-      <x:c r="D39" s="2"/>
-      <x:c r="E39" s="2"/>
-      <x:c r="F39" s="2"/>
-      <x:c r="G39" s="2"/>
-      <x:c r="H39" s="2"/>
-      <x:c r="I39" s="2"/>
-      <x:c r="J39" s="2"/>
-      <x:c r="K39" s="2"/>
-      <x:c r="L39" s="2"/>
-      <x:c r="M39" s="2"/>
-      <x:c r="N39" s="2"/>
-      <x:c r="O39" s="2"/>
-      <x:c r="P39" s="2"/>
-      <x:c r="Q39" s="16"/>
+      <x:c r="A39" s="15" t="str">
+        <x:v>PRPSTFPT43</x:v>
+      </x:c>
+      <x:c r="B39" s="2" t="str">
+        <x:v>Foc Doim Lhr</x:v>
+      </x:c>
+      <x:c r="C39" s="2" t="str">
+        <x:v>Pending From Linkage Officer</x:v>
+      </x:c>
+      <x:c r="D39" s="2" t="str">
+        <x:v>21 July 2026</x:v>
+      </x:c>
+      <x:c r="E39" s="2" t="str">
+        <x:v>2026-05</x:v>
+      </x:c>
+      <x:c r="F39" s="2" t="str">
+        <x:v>Lahore Campus</x:v>
+      </x:c>
+      <x:c r="G39" s="2" t="str">
+        <x:v>Faculty of Management Sciences</x:v>
+      </x:c>
+      <x:c r="H39" s="2" t="str">
+        <x:v>Department of Information Management</x:v>
+      </x:c>
+      <x:c r="I39" s="2" t="str">
+        <x:v>Foc Doim Lhr</x:v>
+      </x:c>
+      <x:c r="J39" s="2" t="str"/>
+      <x:c r="K39" s="2" t="str">
+        <x:v>Guest Lecture / GLIT</x:v>
+      </x:c>
+      <x:c r="L39" s="2" t="str">
+        <x:v>GLIT</x:v>
+      </x:c>
+      <x:c r="M39" s="2" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="N39" s="2" t="str">
+        <x:v>UOL</x:v>
+      </x:c>
+      <x:c r="O39" s="2" t="str">
+        <x:v>Yes</x:v>
+      </x:c>
+      <x:c r="P39" s="2" t="str">
+        <x:v>Yes</x:v>
+      </x:c>
+      <x:c r="Q39" s="16" t="str">
+        <x:v>Ms Rimsha Qayyum delivered a lectur on Qualitative Research Methods. Activity Concluded.</x:v>
+      </x:c>
     </x:row>
     <x:row r="40" ht="27.600000381469727">
       <x:c r="A40" s="15"/>
@@ -33754,61 +35262,563 @@
       </x:c>
     </x:row>
     <x:row r="28" ht="207">
-      <x:c r="A28" s="15"/>
-      <x:c r="B28" s="2"/>
-      <x:c r="C28" s="2"/>
-      <x:c r="D28" s="2"/>
-      <x:c r="E28" s="2"/>
-      <x:c r="F28" s="2"/>
-      <x:c r="G28" s="2"/>
-      <x:c r="H28" s="2"/>
-      <x:c r="I28" s="2"/>
-      <x:c r="J28" s="2"/>
-      <x:c r="K28" s="2"/>
-      <x:c r="L28" s="2"/>
-      <x:c r="M28" s="2"/>
-      <x:c r="N28" s="2"/>
-      <x:c r="O28" s="2"/>
-      <x:c r="P28" s="2"/>
-      <x:c r="Q28" s="16"/>
+      <x:c r="A28" s="15" t="str">
+        <x:v>PRPSTFPT103</x:v>
+      </x:c>
+      <x:c r="B28" s="2" t="str">
+        <x:v>Foc Soca Lhr</x:v>
+      </x:c>
+      <x:c r="C28" s="2" t="str">
+        <x:v>Pending From Linkage Officer</x:v>
+      </x:c>
+      <x:c r="D28" s="2" t="str">
+        <x:v>7 October 2026</x:v>
+      </x:c>
+      <x:c r="E28" s="2" t="str">
+        <x:v>2026-10</x:v>
+      </x:c>
+      <x:c r="F28" s="2" t="str">
+        <x:v>Lahore Campus</x:v>
+      </x:c>
+      <x:c r="G28" s="2" t="str">
+        <x:v>Faculty of Arts and Architecture</x:v>
+      </x:c>
+      <x:c r="H28" s="2" t="str">
+        <x:v>School of Creative Arts</x:v>
+      </x:c>
+      <x:c r="I28" s="2" t="str">
+        <x:v>Foc Soca Lhr</x:v>
+      </x:c>
+      <x:c r="J28" s="2" t="str"/>
+      <x:c r="K28" s="2" t="str">
+        <x:v>Industrial Visit / IV</x:v>
+      </x:c>
+      <x:c r="L28" s="2" t="str">
+        <x:v>Industrial Visit</x:v>
+      </x:c>
+      <x:c r="M28" s="2" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="N28" s="2" t="str">
+        <x:v>Punjab Safe Cities</x:v>
+      </x:c>
+      <x:c r="O28" s="2" t="str">
+        <x:v>Yes</x:v>
+      </x:c>
+      <x:c r="P28" s="2" t="str">
+        <x:v>Yes</x:v>
+      </x:c>
+      <x:c r="Q28" s="16" t="str">
+        <x:v>Planned</x:v>
+      </x:c>
     </x:row>
     <x:row r="29" ht="27.600000381469727">
-      <x:c r="A29" s="15"/>
-      <x:c r="B29" s="2"/>
-      <x:c r="C29" s="2"/>
-      <x:c r="D29" s="2"/>
+      <x:c r="A29" s="15" t="str">
+        <x:v>PRPSTFPT103</x:v>
+      </x:c>
+      <x:c r="B29" s="2" t="str">
+        <x:v>Foc Soca Lhr</x:v>
+      </x:c>
+      <x:c r="C29" s="2" t="str">
+        <x:v>Pending From Linkage Officer</x:v>
+      </x:c>
+      <x:c r="D29" s="2" t="str">
+        <x:v>7 October 2026</x:v>
+      </x:c>
       <x:c r="E29" s="2"/>
-      <x:c r="F29" s="2"/>
-      <x:c r="G29" s="2"/>
-      <x:c r="H29" s="2"/>
-      <x:c r="I29" s="2"/>
-      <x:c r="J29" s="2"/>
-      <x:c r="K29" s="2"/>
-      <x:c r="L29" s="2"/>
-      <x:c r="M29" s="2"/>
-      <x:c r="N29" s="2"/>
-      <x:c r="O29" s="2"/>
-      <x:c r="P29" s="2"/>
-      <x:c r="Q29" s="16"/>
+      <x:c r="F29" s="2" t="str">
+        <x:v>Lahore Campus</x:v>
+      </x:c>
+      <x:c r="G29" s="2" t="str">
+        <x:v>Faculty of Arts and Architecture</x:v>
+      </x:c>
+      <x:c r="H29" s="2" t="str">
+        <x:v>School of Creative Arts</x:v>
+      </x:c>
+      <x:c r="I29" s="2" t="str">
+        <x:v>Foc Soca Lhr</x:v>
+      </x:c>
+      <x:c r="J29" s="2" t="str"/>
+      <x:c r="K29" s="2" t="str">
+        <x:v>Industrial Visit / IV</x:v>
+      </x:c>
+      <x:c r="L29" s="2" t="str">
+        <x:v>Industrial Visit</x:v>
+      </x:c>
+      <x:c r="M29" s="2" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="N29" s="2" t="str">
+        <x:v>Radio Broadcasting Station Lahore</x:v>
+      </x:c>
+      <x:c r="O29" s="2" t="str">
+        <x:v>Yes</x:v>
+      </x:c>
+      <x:c r="P29" s="2" t="str">
+        <x:v>Yes</x:v>
+      </x:c>
+      <x:c r="Q29" s="16" t="str">
+        <x:v>Inprogress</x:v>
+      </x:c>
     </x:row>
     <x:row r="30">
-      <x:c r="A30" s="17"/>
-      <x:c r="B30" s="18"/>
-      <x:c r="C30" s="18"/>
-      <x:c r="D30" s="18"/>
-      <x:c r="E30" s="18"/>
-      <x:c r="F30" s="18"/>
-      <x:c r="G30" s="18"/>
-      <x:c r="H30" s="18"/>
-      <x:c r="I30" s="18"/>
-      <x:c r="J30" s="18"/>
-      <x:c r="K30" s="18"/>
-      <x:c r="L30" s="18"/>
-      <x:c r="M30" s="18"/>
-      <x:c r="N30" s="18"/>
-      <x:c r="O30" s="18"/>
-      <x:c r="P30" s="18"/>
-      <x:c r="Q30" s="19"/>
+      <x:c r="A30" s="17" t="str">
+        <x:v>PRPSTFPT103</x:v>
+      </x:c>
+      <x:c r="B30" s="18" t="str">
+        <x:v>Foc Soca Lhr</x:v>
+      </x:c>
+      <x:c r="C30" s="18" t="str">
+        <x:v>Pending From Linkage Officer</x:v>
+      </x:c>
+      <x:c r="D30" s="18" t="str">
+        <x:v>7 October 2026</x:v>
+      </x:c>
+      <x:c r="E30" s="18" t="str">
+        <x:v>2026-11</x:v>
+      </x:c>
+      <x:c r="F30" s="18" t="str">
+        <x:v>Lahore Campus</x:v>
+      </x:c>
+      <x:c r="G30" s="18" t="str">
+        <x:v>Faculty of Arts and Architecture</x:v>
+      </x:c>
+      <x:c r="H30" s="18" t="str">
+        <x:v>School of Creative Arts</x:v>
+      </x:c>
+      <x:c r="I30" s="18" t="str">
+        <x:v>Foc Soca Lhr</x:v>
+      </x:c>
+      <x:c r="J30" s="18" t="str"/>
+      <x:c r="K30" s="18" t="str">
+        <x:v>Industrial Visit / IV</x:v>
+      </x:c>
+      <x:c r="L30" s="18" t="str">
+        <x:v>Industrial Visit</x:v>
+      </x:c>
+      <x:c r="M30" s="18" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="N30" s="18" t="str">
+        <x:v>Industrial visit to the Directorate General Public Relations</x:v>
+      </x:c>
+      <x:c r="O30" s="18" t="str">
+        <x:v>Yes</x:v>
+      </x:c>
+      <x:c r="P30" s="18" t="str">
+        <x:v>Yes</x:v>
+      </x:c>
+      <x:c r="Q30" s="19" t="str">
+        <x:v>In progress</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="31">
+      <x:c r="A31" t="str">
+        <x:v>PRPSTFPT103</x:v>
+      </x:c>
+      <x:c r="B31" t="str">
+        <x:v>Foc Soca Lhr</x:v>
+      </x:c>
+      <x:c r="C31" t="str">
+        <x:v>Pending From Linkage Officer</x:v>
+      </x:c>
+      <x:c r="D31" t="str">
+        <x:v>7 October 2026</x:v>
+      </x:c>
+      <x:c r="E31" t="str">
+        <x:v>2026-09</x:v>
+      </x:c>
+      <x:c r="F31" t="str">
+        <x:v>Lahore Campus</x:v>
+      </x:c>
+      <x:c r="G31" t="str">
+        <x:v>Faculty of Arts and Architecture</x:v>
+      </x:c>
+      <x:c r="H31" t="str">
+        <x:v>School of Creative Arts</x:v>
+      </x:c>
+      <x:c r="I31" t="str">
+        <x:v>Foc Soca Lhr</x:v>
+      </x:c>
+      <x:c r="J31" t="str"/>
+      <x:c r="K31" t="str">
+        <x:v>Industrial Visit / IV</x:v>
+      </x:c>
+      <x:c r="L31" t="str">
+        <x:v>Industrial Visit</x:v>
+      </x:c>
+      <x:c r="M31" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="N31" t="str">
+        <x:v>Alhamra Arts Council</x:v>
+      </x:c>
+      <x:c r="O31" t="str">
+        <x:v>Yes</x:v>
+      </x:c>
+      <x:c r="P31" t="str">
+        <x:v>Yes</x:v>
+      </x:c>
+      <x:c r="Q31" t="str">
+        <x:v>Completed</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="32">
+      <x:c r="A32" t="str">
+        <x:v>PRPSTFPT103</x:v>
+      </x:c>
+      <x:c r="B32" t="str">
+        <x:v>Foc Soca Lhr</x:v>
+      </x:c>
+      <x:c r="C32" t="str">
+        <x:v>Pending From Linkage Officer</x:v>
+      </x:c>
+      <x:c r="D32" t="str">
+        <x:v>7 October 2026</x:v>
+      </x:c>
+      <x:c r="E32" t="str">
+        <x:v>2026-11</x:v>
+      </x:c>
+      <x:c r="F32" t="str">
+        <x:v>Lahore Campus</x:v>
+      </x:c>
+      <x:c r="G32" t="str">
+        <x:v>Faculty of Arts and Architecture</x:v>
+      </x:c>
+      <x:c r="H32" t="str">
+        <x:v>School of Creative Arts</x:v>
+      </x:c>
+      <x:c r="I32" t="str">
+        <x:v>Foc Soca Lhr</x:v>
+      </x:c>
+      <x:c r="J32" t="str"/>
+      <x:c r="K32" t="str">
+        <x:v>Industrial Visit / IV</x:v>
+      </x:c>
+      <x:c r="L32" t="str">
+        <x:v>Industrial Visit</x:v>
+      </x:c>
+      <x:c r="M32" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="N32" t="str">
+        <x:v>Buddah Caves</x:v>
+      </x:c>
+      <x:c r="O32" t="str">
+        <x:v>Yes</x:v>
+      </x:c>
+      <x:c r="P32" t="str">
+        <x:v>Yes</x:v>
+      </x:c>
+      <x:c r="Q32" t="str">
+        <x:v>Inprogress</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="33">
+      <x:c r="A33" t="str">
+        <x:v>PRPSTFPT103</x:v>
+      </x:c>
+      <x:c r="B33" t="str">
+        <x:v>Foc Soca Lhr</x:v>
+      </x:c>
+      <x:c r="C33" t="str">
+        <x:v>Pending From Linkage Officer</x:v>
+      </x:c>
+      <x:c r="D33" t="str">
+        <x:v>7 October 2026</x:v>
+      </x:c>
+      <x:c r="E33" t="str">
+        <x:v>2026-10</x:v>
+      </x:c>
+      <x:c r="F33" t="str">
+        <x:v>Lahore Campus</x:v>
+      </x:c>
+      <x:c r="G33" t="str">
+        <x:v>Faculty of Arts and Architecture</x:v>
+      </x:c>
+      <x:c r="H33" t="str">
+        <x:v>School of Creative Arts</x:v>
+      </x:c>
+      <x:c r="I33" t="str">
+        <x:v>Foc Soca Lhr</x:v>
+      </x:c>
+      <x:c r="J33" t="str"/>
+      <x:c r="K33" t="str">
+        <x:v>Industrial Visit / IV</x:v>
+      </x:c>
+      <x:c r="L33" t="str">
+        <x:v>Industrial Visit</x:v>
+      </x:c>
+      <x:c r="M33" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="N33" t="str">
+        <x:v>OArt space</x:v>
+      </x:c>
+      <x:c r="O33" t="str">
+        <x:v>Yes</x:v>
+      </x:c>
+      <x:c r="P33" t="str">
+        <x:v>Yes</x:v>
+      </x:c>
+      <x:c r="Q33" t="str">
+        <x:v>Inprogress</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="34">
+      <x:c r="A34" t="str">
+        <x:v>PRPSTFPT103</x:v>
+      </x:c>
+      <x:c r="B34" t="str">
+        <x:v>Foc Soca Lhr</x:v>
+      </x:c>
+      <x:c r="C34" t="str">
+        <x:v>Pending From Linkage Officer</x:v>
+      </x:c>
+      <x:c r="D34" t="str">
+        <x:v>7 October 2026</x:v>
+      </x:c>
+      <x:c r="E34" t="str">
+        <x:v>2026-11</x:v>
+      </x:c>
+      <x:c r="F34" t="str">
+        <x:v>Lahore Campus</x:v>
+      </x:c>
+      <x:c r="G34" t="str">
+        <x:v>Faculty of Arts and Architecture</x:v>
+      </x:c>
+      <x:c r="H34" t="str">
+        <x:v>School of Creative Arts</x:v>
+      </x:c>
+      <x:c r="I34" t="str">
+        <x:v>Foc Soca Lhr</x:v>
+      </x:c>
+      <x:c r="J34" t="str"/>
+      <x:c r="K34" t="str">
+        <x:v>Industrial Visit / IV</x:v>
+      </x:c>
+      <x:c r="L34" t="str">
+        <x:v>Industrial Visit</x:v>
+      </x:c>
+      <x:c r="M34" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="N34" t="str">
+        <x:v>Cobalt gallery</x:v>
+      </x:c>
+      <x:c r="O34" t="str">
+        <x:v>Yes</x:v>
+      </x:c>
+      <x:c r="P34" t="str">
+        <x:v>Yes</x:v>
+      </x:c>
+      <x:c r="Q34" t="str">
+        <x:v>planned</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="35">
+      <x:c r="A35" t="str">
+        <x:v>PRPSTFPT103</x:v>
+      </x:c>
+      <x:c r="B35" t="str">
+        <x:v>Foc Soca Lhr</x:v>
+      </x:c>
+      <x:c r="C35" t="str">
+        <x:v>Pending From Linkage Officer</x:v>
+      </x:c>
+      <x:c r="D35" t="str">
+        <x:v>7 October 2026</x:v>
+      </x:c>
+      <x:c r="E35" t="str">
+        <x:v>2026-11</x:v>
+      </x:c>
+      <x:c r="F35" t="str">
+        <x:v>Lahore Campus</x:v>
+      </x:c>
+      <x:c r="G35" t="str">
+        <x:v>Faculty of Arts and Architecture</x:v>
+      </x:c>
+      <x:c r="H35" t="str">
+        <x:v>School of Creative Arts</x:v>
+      </x:c>
+      <x:c r="I35" t="str">
+        <x:v>Foc Soca Lhr</x:v>
+      </x:c>
+      <x:c r="J35" t="str"/>
+      <x:c r="K35" t="str">
+        <x:v>Industrial Visit / IV</x:v>
+      </x:c>
+      <x:c r="L35" t="str">
+        <x:v>Industrial Visit</x:v>
+      </x:c>
+      <x:c r="M35" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="N35" t="str">
+        <x:v>CEGA Centre of Excellence in Gaming and Animation</x:v>
+      </x:c>
+      <x:c r="O35" t="str">
+        <x:v>Yes</x:v>
+      </x:c>
+      <x:c r="P35" t="str">
+        <x:v>Yes</x:v>
+      </x:c>
+      <x:c r="Q35" t="str">
+        <x:v>Inprogress</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="36">
+      <x:c r="A36" t="str">
+        <x:v>PRPSTFPT74</x:v>
+      </x:c>
+      <x:c r="B36" t="str">
+        <x:v>Foc Uifsrt Lhr</x:v>
+      </x:c>
+      <x:c r="C36" t="str">
+        <x:v>Pending From Linkage Officer</x:v>
+      </x:c>
+      <x:c r="D36" t="str">
+        <x:v>31 July 2026</x:v>
+      </x:c>
+      <x:c r="E36" t="str">
+        <x:v>2026-04</x:v>
+      </x:c>
+      <x:c r="F36" t="str">
+        <x:v>Lahore Campus</x:v>
+      </x:c>
+      <x:c r="G36" t="str">
+        <x:v>Faculty of Allied Health Sciences</x:v>
+      </x:c>
+      <x:c r="H36" t="str">
+        <x:v>University Institute of Food Science &amp; Technology</x:v>
+      </x:c>
+      <x:c r="I36" t="str">
+        <x:v>Foc Uifsrt Lhr</x:v>
+      </x:c>
+      <x:c r="J36" t="str"/>
+      <x:c r="K36" t="str">
+        <x:v>Industrial Visit / IV</x:v>
+      </x:c>
+      <x:c r="L36" t="str">
+        <x:v>IV</x:v>
+      </x:c>
+      <x:c r="M36" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="N36" t="str">
+        <x:v>Post Harvest Research Center, AARI</x:v>
+      </x:c>
+      <x:c r="O36" t="str">
+        <x:v>Yes</x:v>
+      </x:c>
+      <x:c r="P36" t="str">
+        <x:v>Yes</x:v>
+      </x:c>
+      <x:c r="Q36" t="str">
+        <x:v>Visited and gain practical knowledge</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="37">
+      <x:c r="A37" t="str">
+        <x:v>PRPSTFPT74</x:v>
+      </x:c>
+      <x:c r="B37" t="str">
+        <x:v>Foc Uifsrt Lhr</x:v>
+      </x:c>
+      <x:c r="C37" t="str">
+        <x:v>Pending From Linkage Officer</x:v>
+      </x:c>
+      <x:c r="D37" t="str">
+        <x:v>31 July 2026</x:v>
+      </x:c>
+      <x:c r="E37" t="str">
+        <x:v>2026-04</x:v>
+      </x:c>
+      <x:c r="F37" t="str">
+        <x:v>Lahore Campus</x:v>
+      </x:c>
+      <x:c r="G37" t="str">
+        <x:v>Faculty of Allied Health Sciences</x:v>
+      </x:c>
+      <x:c r="H37" t="str">
+        <x:v>University Institute of Food Science &amp; Technology</x:v>
+      </x:c>
+      <x:c r="I37" t="str">
+        <x:v>Foc Uifsrt Lhr</x:v>
+      </x:c>
+      <x:c r="J37" t="str"/>
+      <x:c r="K37" t="str">
+        <x:v>Industrial Visit / IV</x:v>
+      </x:c>
+      <x:c r="L37" t="str">
+        <x:v>IV</x:v>
+      </x:c>
+      <x:c r="M37" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="N37" t="str">
+        <x:v>Pak Korea Nutrition Center, PKNC, Faisalabad</x:v>
+      </x:c>
+      <x:c r="O37" t="str">
+        <x:v>Yes</x:v>
+      </x:c>
+      <x:c r="P37" t="str">
+        <x:v>Yes</x:v>
+      </x:c>
+      <x:c r="Q37" t="str">
+        <x:v>Look into research opportunities</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="38">
+      <x:c r="A38" t="str">
+        <x:v>PRPSTFPT74</x:v>
+      </x:c>
+      <x:c r="B38" t="str">
+        <x:v>Foc Uifsrt Lhr</x:v>
+      </x:c>
+      <x:c r="C38" t="str">
+        <x:v>Pending From Linkage Officer</x:v>
+      </x:c>
+      <x:c r="D38" t="str">
+        <x:v>31 July 2026</x:v>
+      </x:c>
+      <x:c r="E38" t="str">
+        <x:v>2026-05</x:v>
+      </x:c>
+      <x:c r="F38" t="str">
+        <x:v>Lahore Campus</x:v>
+      </x:c>
+      <x:c r="G38" t="str">
+        <x:v>Faculty of Allied Health Sciences</x:v>
+      </x:c>
+      <x:c r="H38" t="str">
+        <x:v>University Institute of Food Science &amp; Technology</x:v>
+      </x:c>
+      <x:c r="I38" t="str">
+        <x:v>Foc Uifsrt Lhr</x:v>
+      </x:c>
+      <x:c r="J38" t="str"/>
+      <x:c r="K38" t="str">
+        <x:v>Industrial Visit / IV</x:v>
+      </x:c>
+      <x:c r="L38" t="str">
+        <x:v>IV</x:v>
+      </x:c>
+      <x:c r="M38" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="N38" t="str">
+        <x:v>Bonjour Reliance Foods, Lahore</x:v>
+      </x:c>
+      <x:c r="O38" t="str">
+        <x:v>Yes</x:v>
+      </x:c>
+      <x:c r="P38" t="str">
+        <x:v>Yes</x:v>
+      </x:c>
+      <x:c r="Q38" t="str">
+        <x:v>Visited and Gained Practical Knowledge</x:v>
+      </x:c>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -39973,45 +41983,105 @@
       <x:c r="T123"/>
     </x:row>
     <x:row r="124">
-      <x:c r="A124"/>
-      <x:c r="B124"/>
-      <x:c r="C124"/>
-      <x:c r="D124"/>
+      <x:c r="A124" t="str">
+        <x:v>PRPSTFPT103</x:v>
+      </x:c>
+      <x:c r="B124" t="str">
+        <x:v>Foc Soca Lhr</x:v>
+      </x:c>
+      <x:c r="C124" t="str">
+        <x:v>Pending From Linkage Officer</x:v>
+      </x:c>
+      <x:c r="D124" t="str">
+        <x:v>7 October 2026</x:v>
+      </x:c>
       <x:c r="E124"/>
-      <x:c r="F124"/>
-      <x:c r="G124"/>
-      <x:c r="H124"/>
-      <x:c r="I124"/>
-      <x:c r="J124"/>
-      <x:c r="K124"/>
-      <x:c r="L124"/>
-      <x:c r="M124"/>
-      <x:c r="N124"/>
-      <x:c r="O124"/>
-      <x:c r="P124"/>
-      <x:c r="Q124"/>
+      <x:c r="F124" t="str">
+        <x:v>Lahore Campus</x:v>
+      </x:c>
+      <x:c r="G124" t="str">
+        <x:v>Faculty of Arts and Architecture</x:v>
+      </x:c>
+      <x:c r="H124" t="str">
+        <x:v>School of Creative Arts</x:v>
+      </x:c>
+      <x:c r="I124" t="str">
+        <x:v>Foc Soca Lhr</x:v>
+      </x:c>
+      <x:c r="J124" t="str"/>
+      <x:c r="K124" t="str">
+        <x:v>Internship / Placement</x:v>
+      </x:c>
+      <x:c r="L124" t="str">
+        <x:v>Internship/Placement</x:v>
+      </x:c>
+      <x:c r="M124" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="N124" t="str">
+        <x:v>DGPR</x:v>
+      </x:c>
+      <x:c r="O124" t="str">
+        <x:v>Yes</x:v>
+      </x:c>
+      <x:c r="P124" t="str">
+        <x:v>Yes</x:v>
+      </x:c>
+      <x:c r="Q124" t="str">
+        <x:v>Senior Students</x:v>
+      </x:c>
       <x:c r="R124"/>
       <x:c r="S124"/>
       <x:c r="T124"/>
     </x:row>
     <x:row r="125">
-      <x:c r="A125"/>
-      <x:c r="B125"/>
-      <x:c r="C125"/>
-      <x:c r="D125"/>
+      <x:c r="A125" t="str">
+        <x:v>PRPSTFPT103</x:v>
+      </x:c>
+      <x:c r="B125" t="str">
+        <x:v>Foc Soca Lhr</x:v>
+      </x:c>
+      <x:c r="C125" t="str">
+        <x:v>Pending From Linkage Officer</x:v>
+      </x:c>
+      <x:c r="D125" t="str">
+        <x:v>7 October 2026</x:v>
+      </x:c>
       <x:c r="E125"/>
-      <x:c r="F125"/>
-      <x:c r="G125"/>
-      <x:c r="H125"/>
-      <x:c r="I125"/>
-      <x:c r="J125"/>
-      <x:c r="K125"/>
-      <x:c r="L125"/>
-      <x:c r="M125"/>
-      <x:c r="N125"/>
-      <x:c r="O125"/>
-      <x:c r="P125"/>
-      <x:c r="Q125"/>
+      <x:c r="F125" t="str">
+        <x:v>Lahore Campus</x:v>
+      </x:c>
+      <x:c r="G125" t="str">
+        <x:v>Faculty of Arts and Architecture</x:v>
+      </x:c>
+      <x:c r="H125" t="str">
+        <x:v>School of Creative Arts</x:v>
+      </x:c>
+      <x:c r="I125" t="str">
+        <x:v>Foc Soca Lhr</x:v>
+      </x:c>
+      <x:c r="J125" t="str"/>
+      <x:c r="K125" t="str">
+        <x:v>Internship / Placement</x:v>
+      </x:c>
+      <x:c r="L125" t="str">
+        <x:v>Internship/Placement</x:v>
+      </x:c>
+      <x:c r="M125" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="N125" t="str">
+        <x:v>New Channels</x:v>
+      </x:c>
+      <x:c r="O125" t="str">
+        <x:v>Yes</x:v>
+      </x:c>
+      <x:c r="P125" t="str">
+        <x:v>Yes</x:v>
+      </x:c>
+      <x:c r="Q125" t="str">
+        <x:v>Senior Students + Junior Students</x:v>
+      </x:c>
       <x:c r="R125"/>
       <x:c r="S125"/>
       <x:c r="T125"/>
@@ -41202,6 +43272,57 @@
       </x:c>
       <x:c r="Q24" t="s">
         <x:v>318</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="25">
+      <x:c r="A25" t="str">
+        <x:v>PRPSTFPT103</x:v>
+      </x:c>
+      <x:c r="B25" t="str">
+        <x:v>Foc Soca Lhr</x:v>
+      </x:c>
+      <x:c r="C25" t="str">
+        <x:v>Pending From Linkage Officer</x:v>
+      </x:c>
+      <x:c r="D25" t="str">
+        <x:v>7 October 2026</x:v>
+      </x:c>
+      <x:c r="E25" t="str">
+        <x:v>2026-12</x:v>
+      </x:c>
+      <x:c r="F25" t="str">
+        <x:v>Lahore Campus</x:v>
+      </x:c>
+      <x:c r="G25" t="str">
+        <x:v>Faculty of Arts and Architecture</x:v>
+      </x:c>
+      <x:c r="H25" t="str">
+        <x:v>School of Creative Arts</x:v>
+      </x:c>
+      <x:c r="I25" t="str">
+        <x:v>Foc Soca Lhr</x:v>
+      </x:c>
+      <x:c r="J25" t="str"/>
+      <x:c r="K25" t="str">
+        <x:v>MoU / MoU Signing</x:v>
+      </x:c>
+      <x:c r="L25" t="str">
+        <x:v>MoU Signing</x:v>
+      </x:c>
+      <x:c r="M25" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="N25" t="str">
+        <x:v>Interactive Resource Centre</x:v>
+      </x:c>
+      <x:c r="O25" t="str">
+        <x:v>Yes</x:v>
+      </x:c>
+      <x:c r="P25" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="Q25" t="str">
+        <x:v>Inprogress</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -45220,6 +47341,108 @@
 </x:worksheet>
 </file>
 
+<file path=xl/worksheets/sheet29.xml><?xml version="1.0" encoding="utf-8"?>
+<x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:sheetFormatPr defaultRowHeight="15"/>
+  <x:cols>
+    <x:col min="1" max="1" width="19" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="38" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="70" hidden="0" customWidth="1"/>
+  </x:cols>
+  <x:sheetData>
+    <x:row r="1">
+      <x:c r="A1" s="66" t="str">
+        <x:v>Source Ref</x:v>
+      </x:c>
+      <x:c r="B1" s="66" t="str">
+        <x:v>Decision</x:v>
+      </x:c>
+      <x:c r="C1" s="66" t="str">
+        <x:v>Description</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="2">
+      <x:c r="A2" t="str">
+        <x:v>PRPSTFPT99</x:v>
+      </x:c>
+      <x:c r="B2" t="str">
+        <x:v>Repeated event (retained PRPSTFPT100)</x:v>
+      </x:c>
+      <x:c r="C2" t="str">
+        <x:v>T</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="3">
+      <x:c r="A3" t="str">
+        <x:v>PRPSTFPT98</x:v>
+      </x:c>
+      <x:c r="B3" t="str">
+        <x:v>Repeated event (retained PRPSTFPT100)</x:v>
+      </x:c>
+      <x:c r="C3" t="str">
+        <x:v>T</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="4">
+      <x:c r="A4" t="str">
+        <x:v>PRPSTFPT74</x:v>
+      </x:c>
+      <x:c r="B4" t="str">
+        <x:v>Incomplete activity entry</x:v>
+      </x:c>
+      <x:c r="C4" t="str">
+        <x:v>Activity Type: IV, How Many: 1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="5">
+      <x:c r="A5" t="str">
+        <x:v>PRPSTFPT99</x:v>
+      </x:c>
+      <x:c r="B5" t="str">
+        <x:v>Repeated MoU partner (retained PRPSTFPT100)</x:v>
+      </x:c>
+      <x:c r="C5" t="str">
+        <x:v>The Golden Ring Economic Forum</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="6">
+      <x:c r="A6" t="str">
+        <x:v>PRPSTFPT99</x:v>
+      </x:c>
+      <x:c r="B6" t="str">
+        <x:v>Repeated MoU partner (retained PRPSTFPT100)</x:v>
+      </x:c>
+      <x:c r="C6" t="str">
+        <x:v>Consortium for Asia Pacific &amp; Eurasian Studies (CAPES)</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="7">
+      <x:c r="A7" t="str">
+        <x:v>PRPSTFPT98</x:v>
+      </x:c>
+      <x:c r="B7" t="str">
+        <x:v>Repeated MoU partner (retained PRPSTFPT100)</x:v>
+      </x:c>
+      <x:c r="C7" t="str">
+        <x:v>The Golden Ring Economic Forum</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="8">
+      <x:c r="A8" t="str">
+        <x:v>PRPSTFPT98</x:v>
+      </x:c>
+      <x:c r="B8" t="str">
+        <x:v>Repeated MoU partner (retained PRPSTFPT100)</x:v>
+      </x:c>
+      <x:c r="C8" t="str">
+        <x:v>Consortium for Asia Pacific &amp; Eurasian Studies (CAPES)</x:v>
+      </x:c>
+    </x:row>
+  </x:sheetData>
+  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</x:worksheet>
+</file>
+
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetFormatPr defaultRowHeight="13.800000190734863"/>

--- a/data/UOL_Separated_All_Activity_Data_Cleaned.xlsx
+++ b/data/UOL_Separated_All_Activity_Data_Cleaned.xlsx
@@ -2,35 +2,35 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" r:id="R254fcf0707f14603"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="All Separated Activities" sheetId="2" r:id="R0ff161b39f9f4108"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Alumni Talk - Mentoring" sheetId="3" r:id="R8e077d3efe524c9a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Community Engagement" sheetId="4" r:id="R6f870b772ce544cb"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Conference" sheetId="5" r:id="Rd1dd04a776604b6b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Curriculum Feedback Session" sheetId="6" r:id="Reea80e88705242a6"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="GLIT" sheetId="7" r:id="Rb8dea917cabc4dea"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Guest Lecture" sheetId="8" r:id="R372c9943ed5d49ac"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IAB Meeting - Industry Consulta" sheetId="9" r:id="Rb39b2b36222e4698"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IP" sheetId="10" r:id="R3436c527e39844ca"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IV" sheetId="11" r:id="Rce687c8fe3ff416c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Industrial Visit" sheetId="12" r:id="R06c4795162524bfd"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Internship-Placement" sheetId="13" r:id="R679e0375263b4cbb"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="MOU" sheetId="14" r:id="R05f50b10cc3c4345"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="MoU Signing (Memorandum of Unde" sheetId="15" r:id="R5495ea235b084009"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Others" sheetId="16" r:id="Re515b627cdae4300"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Research Collaboration" sheetId="17" r:id="Rd747a4bc24bd4e8c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Seminar" sheetId="18" r:id="Recc39b42c7b44d39"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Unclassified" sheetId="19" r:id="Rc847df97cd254815"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Workshop" sheetId="20" r:id="R5dbe73ef404843c6"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Guest Lecture - GLIT" sheetId="21" r:id="R83cb4464d8024eb5"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Industrial Visit - IV" sheetId="22" r:id="R9b52c0ace2634762"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Internship - Placement" sheetId="23" r:id="R700da3f079534665"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="MoU - MoU Signing" sheetId="24" r:id="R8bec06de9ade4023"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="New Data Added" sheetId="25" r:id="R5c050ecb491d4656"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Planned - Section 4" sheetId="26" r:id="R7a48526c905a491d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Planned Activities" sheetId="27" r:id="R3d0ce12679e34be7"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Remote Activities" sheetId="28" r:id="R08e078c46319483c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="64 Submission Reconciliation" sheetId="29" r:id="R5700745502b94342"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" r:id="R0c58bcb6b34048e6"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="All Separated Activities" sheetId="2" r:id="R8b6373e6feb24d40"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Alumni Talk - Mentoring" sheetId="3" r:id="R9a7bdbfb3e734673"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Community Engagement" sheetId="4" r:id="R09bc3854be64413c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Conference" sheetId="5" r:id="Rba5a5e39611047e6"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Curriculum Feedback Session" sheetId="6" r:id="R8884e0e2aa0c48f1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="GLIT" sheetId="7" r:id="R023c4dacb98d4b71"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Guest Lecture" sheetId="8" r:id="Rbcee8ab9156548be"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IAB Meeting - Industry Consulta" sheetId="9" r:id="Rf79250df3988410f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IP" sheetId="10" r:id="R53d076185dec4c6d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IV" sheetId="11" r:id="R53aa8f0767394940"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Industrial Visit" sheetId="12" r:id="R974e6294a1b043c6"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Internship-Placement" sheetId="13" r:id="R4f0c77b98549429c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="MOU" sheetId="14" r:id="R458dc294c58247a6"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="MoU Signing (Memorandum of Unde" sheetId="15" r:id="R3a652f5ef613428c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Others" sheetId="16" r:id="R5d5ae77d1d154701"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Research Collaboration" sheetId="17" r:id="Rb3b5f38aa90e4787"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Seminar" sheetId="18" r:id="R07555fbaa74e4ea0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Unclassified" sheetId="19" r:id="R6509a6b99a634ce1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Workshop" sheetId="20" r:id="Rb5713055d8f04258"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Guest Lecture - GLIT" sheetId="21" r:id="R12dd0b22f0dc461f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Industrial Visit - IV" sheetId="22" r:id="R43cd131aa5da4c26"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Internship - Placement" sheetId="23" r:id="Rc61fca62683e4c40"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="MoU - MoU Signing" sheetId="24" r:id="Rb4d33ff4bc9a48e3"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="New Data Added" sheetId="25" r:id="R00a58db3d7854321"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Planned - Section 4" sheetId="26" r:id="Rabfb1e31dd4241c1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Planned Activities" sheetId="27" r:id="Rf52ff2497fcf4119"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Remote Activities" sheetId="28" r:id="Rade993eb4b034e58"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="64 Submission Reconciliation" sheetId="29" r:id="R55a5037ce846417a"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -1979,10 +1979,10 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="B6" t="n">
-        <x:v>33</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="C6" s="8" t="n">
-        <x:v>125</x:v>
+        <x:v>130</x:v>
       </x:c>
     </x:row>
     <x:row r="7">
@@ -2056,10 +2056,10 @@
         <x:v>16</x:v>
       </x:c>
       <x:c r="B13" t="n">
-        <x:v>27</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="C13" s="8" t="n">
-        <x:v>82</x:v>
+        <x:v>84</x:v>
       </x:c>
     </x:row>
     <x:row r="14">
@@ -14422,6 +14422,112 @@
         <x:v>The webinar on Intelligent Literature Reviews: AI Tools, Critical Thinking, and Research Ethics,  Prof. Dr. Zaheer Ahmad, Resource Person, discussed the significance of literature reviews in identifying research gaps and building a strong scholarly foundation. He demonstrated how AI-powered tools can support literature searching, evidence synthesis, summarization, reference management, and academic writing while emphasizing that researchers must apply critical thinking, sound judgment, and ethical practices throughout the research process. He also stressed the importance of verifying AI-generated content, avoiding plagiarism and fabricated citations, and ensuring transparency in the responsible use of AI.</x:v>
       </x:c>
     </x:row>
+    <x:row r="35">
+      <x:c r="A35" t="str">
+        <x:v>PRPSTFPT105</x:v>
+      </x:c>
+      <x:c r="B35" t="str">
+        <x:v>Foc Pharm Lhr</x:v>
+      </x:c>
+      <x:c r="C35" t="str">
+        <x:v>Pending From Linkage Officer</x:v>
+      </x:c>
+      <x:c r="D35" t="str">
+        <x:v>12 October 2026</x:v>
+      </x:c>
+      <x:c r="E35" t="str">
+        <x:v>2026-10-01</x:v>
+      </x:c>
+      <x:c r="F35" t="str">
+        <x:v>Lahore Campus</x:v>
+      </x:c>
+      <x:c r="G35" t="str">
+        <x:v>Faculty of Pharmacy</x:v>
+      </x:c>
+      <x:c r="H35" t="str">
+        <x:v>Department of Pharmacy</x:v>
+      </x:c>
+      <x:c r="I35" t="str">
+        <x:v>Foc Pharm Lhr</x:v>
+      </x:c>
+      <x:c r="J35" t="str">
+        <x:v>Assistanat Professor</x:v>
+      </x:c>
+      <x:c r="K35" t="str">
+        <x:v>Seminar</x:v>
+      </x:c>
+      <x:c r="L35" t="str">
+        <x:v>Seminar / Conference / Workshop</x:v>
+      </x:c>
+      <x:c r="M35" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="N35" t="str">
+        <x:v>CHughtai LAb</x:v>
+      </x:c>
+      <x:c r="O35" t="str">
+        <x:v>Yes</x:v>
+      </x:c>
+      <x:c r="P35" t="str">
+        <x:v>Yes</x:v>
+      </x:c>
+      <x:c r="Q35" t="str">
+        <x:v>Done; planned date: 2026-09-16</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="36">
+      <x:c r="A36" t="str">
+        <x:v>PRPSTFPT105</x:v>
+      </x:c>
+      <x:c r="B36" t="str">
+        <x:v>Foc Pharm Lhr</x:v>
+      </x:c>
+      <x:c r="C36" t="str">
+        <x:v>Pending From Linkage Officer</x:v>
+      </x:c>
+      <x:c r="D36" t="str">
+        <x:v>12 October 2026</x:v>
+      </x:c>
+      <x:c r="E36" t="str">
+        <x:v>2026-10-01</x:v>
+      </x:c>
+      <x:c r="F36" t="str">
+        <x:v>Lahore Campus</x:v>
+      </x:c>
+      <x:c r="G36" t="str">
+        <x:v>Faculty of Pharmacy</x:v>
+      </x:c>
+      <x:c r="H36" t="str">
+        <x:v>Department of Pharmacy</x:v>
+      </x:c>
+      <x:c r="I36" t="str">
+        <x:v>Foc Pharm Lhr</x:v>
+      </x:c>
+      <x:c r="J36" t="str">
+        <x:v>Assistanat Professor</x:v>
+      </x:c>
+      <x:c r="K36" t="str">
+        <x:v>Seminar</x:v>
+      </x:c>
+      <x:c r="L36" t="str">
+        <x:v>Seminar / Conference / Workshop</x:v>
+      </x:c>
+      <x:c r="M36" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="N36" t="str">
+        <x:v>SKMHRC</x:v>
+      </x:c>
+      <x:c r="O36" t="str">
+        <x:v>Yes</x:v>
+      </x:c>
+      <x:c r="P36" t="str">
+        <x:v>Yes</x:v>
+      </x:c>
+      <x:c r="Q36" t="str">
+        <x:v>Planned date: 2026-10-12</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>
@@ -30775,23 +30881,161 @@
       </x:c>
     </x:row>
     <x:row r="328">
-      <x:c r="A328"/>
-      <x:c r="B328"/>
-      <x:c r="C328"/>
-      <x:c r="D328"/>
-      <x:c r="E328"/>
-      <x:c r="F328"/>
-      <x:c r="G328"/>
-      <x:c r="H328"/>
-      <x:c r="I328"/>
-      <x:c r="J328"/>
-      <x:c r="K328"/>
-      <x:c r="L328"/>
-      <x:c r="M328"/>
-      <x:c r="N328"/>
-      <x:c r="O328"/>
-      <x:c r="P328"/>
-      <x:c r="Q328"/>
+      <x:c r="A328" t="str">
+        <x:v>PRPSTFPT105</x:v>
+      </x:c>
+      <x:c r="B328" t="str">
+        <x:v>Foc Pharm Lhr</x:v>
+      </x:c>
+      <x:c r="C328" t="str">
+        <x:v>Pending From Linkage Officer</x:v>
+      </x:c>
+      <x:c r="D328" t="str">
+        <x:v>12 October 2026</x:v>
+      </x:c>
+      <x:c r="E328" t="str">
+        <x:v>2026-10-01</x:v>
+      </x:c>
+      <x:c r="F328" t="str">
+        <x:v>Lahore Campus</x:v>
+      </x:c>
+      <x:c r="G328" t="str">
+        <x:v>Faculty of Pharmacy</x:v>
+      </x:c>
+      <x:c r="H328" t="str">
+        <x:v>Department of Pharmacy</x:v>
+      </x:c>
+      <x:c r="I328" t="str">
+        <x:v>Foc Pharm Lhr</x:v>
+      </x:c>
+      <x:c r="J328" t="str">
+        <x:v>Assistanat Professor</x:v>
+      </x:c>
+      <x:c r="K328" t="str">
+        <x:v>Seminar</x:v>
+      </x:c>
+      <x:c r="L328" t="str">
+        <x:v>Seminar / Conference / Workshop</x:v>
+      </x:c>
+      <x:c r="M328" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="N328" t="str">
+        <x:v>CHughtai LAb</x:v>
+      </x:c>
+      <x:c r="O328" t="str">
+        <x:v>Yes</x:v>
+      </x:c>
+      <x:c r="P328" t="str">
+        <x:v>Yes</x:v>
+      </x:c>
+      <x:c r="Q328" t="str">
+        <x:v>Done; planned date: 2026-09-16</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="329">
+      <x:c r="A329" t="str">
+        <x:v>PRPSTFPT105</x:v>
+      </x:c>
+      <x:c r="B329" t="str">
+        <x:v>Foc Pharm Lhr</x:v>
+      </x:c>
+      <x:c r="C329" t="str">
+        <x:v>Pending From Linkage Officer</x:v>
+      </x:c>
+      <x:c r="D329" t="str">
+        <x:v>12 October 2026</x:v>
+      </x:c>
+      <x:c r="E329" t="str">
+        <x:v>2026-10-01</x:v>
+      </x:c>
+      <x:c r="F329" t="str">
+        <x:v>Lahore Campus</x:v>
+      </x:c>
+      <x:c r="G329" t="str">
+        <x:v>Faculty of Pharmacy</x:v>
+      </x:c>
+      <x:c r="H329" t="str">
+        <x:v>Department of Pharmacy</x:v>
+      </x:c>
+      <x:c r="I329" t="str">
+        <x:v>Foc Pharm Lhr</x:v>
+      </x:c>
+      <x:c r="J329" t="str">
+        <x:v>Assistanat Professor</x:v>
+      </x:c>
+      <x:c r="K329" t="str">
+        <x:v>Seminar</x:v>
+      </x:c>
+      <x:c r="L329" t="str">
+        <x:v>Seminar / Conference / Workshop</x:v>
+      </x:c>
+      <x:c r="M329" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="N329" t="str">
+        <x:v>SKMHRC</x:v>
+      </x:c>
+      <x:c r="O329" t="str">
+        <x:v>Yes</x:v>
+      </x:c>
+      <x:c r="P329" t="str">
+        <x:v>Yes</x:v>
+      </x:c>
+      <x:c r="Q329" t="str">
+        <x:v>Planned date: 2026-10-12</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="330">
+      <x:c r="A330" t="str">
+        <x:v>PRPSTFPT105</x:v>
+      </x:c>
+      <x:c r="B330" t="str">
+        <x:v>Foc Pharm Lhr</x:v>
+      </x:c>
+      <x:c r="C330" t="str">
+        <x:v>Pending From Linkage Officer</x:v>
+      </x:c>
+      <x:c r="D330" t="str">
+        <x:v>12 October 2026</x:v>
+      </x:c>
+      <x:c r="E330" t="str">
+        <x:v>2026-10-01</x:v>
+      </x:c>
+      <x:c r="F330" t="str">
+        <x:v>Lahore Campus</x:v>
+      </x:c>
+      <x:c r="G330" t="str">
+        <x:v>Faculty of Pharmacy</x:v>
+      </x:c>
+      <x:c r="H330" t="str">
+        <x:v>Department of Pharmacy</x:v>
+      </x:c>
+      <x:c r="I330" t="str">
+        <x:v>Foc Pharm Lhr</x:v>
+      </x:c>
+      <x:c r="J330" t="str">
+        <x:v>Assistanat Professor</x:v>
+      </x:c>
+      <x:c r="K330" t="str">
+        <x:v>Guest Lecture / GLIT</x:v>
+      </x:c>
+      <x:c r="L330" t="str">
+        <x:v>Guest Lecture</x:v>
+      </x:c>
+      <x:c r="M330" t="str">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="N330" t="str">
+        <x:v>Dr Kamala Dr Osman Mirza Dr Khalid Dr Mohsen Dr Hafiz Hassan</x:v>
+      </x:c>
+      <x:c r="O330" t="str">
+        <x:v>Yes</x:v>
+      </x:c>
+      <x:c r="P330" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="Q330"/>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -33526,22 +33770,54 @@
       </x:c>
     </x:row>
     <x:row r="40" ht="27.600000381469727">
-      <x:c r="A40" s="15"/>
-      <x:c r="B40" s="2"/>
-      <x:c r="C40" s="2"/>
-      <x:c r="D40" s="2"/>
-      <x:c r="E40" s="2"/>
-      <x:c r="F40" s="2"/>
-      <x:c r="G40" s="2"/>
-      <x:c r="H40" s="2"/>
-      <x:c r="I40" s="2"/>
-      <x:c r="J40" s="2"/>
-      <x:c r="K40" s="2"/>
-      <x:c r="L40" s="2"/>
-      <x:c r="M40" s="2"/>
-      <x:c r="N40" s="2"/>
-      <x:c r="O40" s="2"/>
-      <x:c r="P40" s="2"/>
+      <x:c r="A40" s="15" t="str">
+        <x:v>PRPSTFPT105</x:v>
+      </x:c>
+      <x:c r="B40" s="2" t="str">
+        <x:v>Foc Pharm Lhr</x:v>
+      </x:c>
+      <x:c r="C40" s="2" t="str">
+        <x:v>Pending From Linkage Officer</x:v>
+      </x:c>
+      <x:c r="D40" s="2" t="str">
+        <x:v>12 October 2026</x:v>
+      </x:c>
+      <x:c r="E40" s="2" t="str">
+        <x:v>2026-10-01</x:v>
+      </x:c>
+      <x:c r="F40" s="2" t="str">
+        <x:v>Lahore Campus</x:v>
+      </x:c>
+      <x:c r="G40" s="2" t="str">
+        <x:v>Faculty of Pharmacy</x:v>
+      </x:c>
+      <x:c r="H40" s="2" t="str">
+        <x:v>Department of Pharmacy</x:v>
+      </x:c>
+      <x:c r="I40" s="2" t="str">
+        <x:v>Foc Pharm Lhr</x:v>
+      </x:c>
+      <x:c r="J40" s="2" t="str">
+        <x:v>Assistanat Professor</x:v>
+      </x:c>
+      <x:c r="K40" s="2" t="str">
+        <x:v>Guest Lecture / GLIT</x:v>
+      </x:c>
+      <x:c r="L40" s="2" t="str">
+        <x:v>Guest Lecture</x:v>
+      </x:c>
+      <x:c r="M40" s="2" t="str">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="N40" s="2" t="str">
+        <x:v>Dr Kamala Dr Osman Mirza Dr Khalid Dr Mohsen Dr Hafiz Hassan</x:v>
+      </x:c>
+      <x:c r="O40" s="2" t="str">
+        <x:v>Yes</x:v>
+      </x:c>
+      <x:c r="P40" s="2" t="str">
+        <x:v>No</x:v>
+      </x:c>
       <x:c r="Q40" s="16"/>
     </x:row>
     <x:row r="41" ht="27.600000381469727">
@@ -50843,22 +51119,54 @@
       </x:c>
     </x:row>
     <x:row r="11">
-      <x:c r="A11" s="2"/>
-      <x:c r="B11" s="2"/>
-      <x:c r="C11" s="2"/>
-      <x:c r="D11" s="2"/>
-      <x:c r="E11" s="2"/>
-      <x:c r="F11" s="2"/>
-      <x:c r="G11" s="2"/>
-      <x:c r="H11" s="2"/>
-      <x:c r="I11" s="2"/>
-      <x:c r="J11" s="2"/>
-      <x:c r="K11" s="2"/>
-      <x:c r="L11" s="2"/>
-      <x:c r="M11" s="2"/>
-      <x:c r="N11" s="2"/>
-      <x:c r="O11" s="2"/>
-      <x:c r="P11" s="2"/>
+      <x:c r="A11" s="2" t="str">
+        <x:v>PRPSTFPT105</x:v>
+      </x:c>
+      <x:c r="B11" s="2" t="str">
+        <x:v>Foc Pharm Lhr</x:v>
+      </x:c>
+      <x:c r="C11" s="2" t="str">
+        <x:v>Pending From Linkage Officer</x:v>
+      </x:c>
+      <x:c r="D11" s="2" t="str">
+        <x:v>12 October 2026</x:v>
+      </x:c>
+      <x:c r="E11" s="2" t="str">
+        <x:v>2026-10-01</x:v>
+      </x:c>
+      <x:c r="F11" s="2" t="str">
+        <x:v>Lahore Campus</x:v>
+      </x:c>
+      <x:c r="G11" s="2" t="str">
+        <x:v>Faculty of Pharmacy</x:v>
+      </x:c>
+      <x:c r="H11" s="2" t="str">
+        <x:v>Department of Pharmacy</x:v>
+      </x:c>
+      <x:c r="I11" s="2" t="str">
+        <x:v>Foc Pharm Lhr</x:v>
+      </x:c>
+      <x:c r="J11" s="2" t="str">
+        <x:v>Assistanat Professor</x:v>
+      </x:c>
+      <x:c r="K11" s="2" t="str">
+        <x:v>Guest Lecture / GLIT</x:v>
+      </x:c>
+      <x:c r="L11" s="2" t="str">
+        <x:v>Guest Lecture</x:v>
+      </x:c>
+      <x:c r="M11" s="2" t="str">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="N11" s="2" t="str">
+        <x:v>Dr Kamala Dr Osman Mirza Dr Khalid Dr Mohsen Dr Hafiz Hassan</x:v>
+      </x:c>
+      <x:c r="O11" s="2" t="str">
+        <x:v>Yes</x:v>
+      </x:c>
+      <x:c r="P11" s="2" t="str">
+        <x:v>No</x:v>
+      </x:c>
       <x:c r="Q11" s="2"/>
     </x:row>
     <x:row r="12">

--- a/data/UOL_Separated_All_Activity_Data_Cleaned.xlsx
+++ b/data/UOL_Separated_All_Activity_Data_Cleaned.xlsx
@@ -2,35 +2,35 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" r:id="R0c58bcb6b34048e6"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="All Separated Activities" sheetId="2" r:id="R8b6373e6feb24d40"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Alumni Talk - Mentoring" sheetId="3" r:id="R9a7bdbfb3e734673"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Community Engagement" sheetId="4" r:id="R09bc3854be64413c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Conference" sheetId="5" r:id="Rba5a5e39611047e6"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Curriculum Feedback Session" sheetId="6" r:id="R8884e0e2aa0c48f1"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="GLIT" sheetId="7" r:id="R023c4dacb98d4b71"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Guest Lecture" sheetId="8" r:id="Rbcee8ab9156548be"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IAB Meeting - Industry Consulta" sheetId="9" r:id="Rf79250df3988410f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IP" sheetId="10" r:id="R53d076185dec4c6d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IV" sheetId="11" r:id="R53aa8f0767394940"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Industrial Visit" sheetId="12" r:id="R974e6294a1b043c6"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Internship-Placement" sheetId="13" r:id="R4f0c77b98549429c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="MOU" sheetId="14" r:id="R458dc294c58247a6"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="MoU Signing (Memorandum of Unde" sheetId="15" r:id="R3a652f5ef613428c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Others" sheetId="16" r:id="R5d5ae77d1d154701"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Research Collaboration" sheetId="17" r:id="Rb3b5f38aa90e4787"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Seminar" sheetId="18" r:id="R07555fbaa74e4ea0"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Unclassified" sheetId="19" r:id="R6509a6b99a634ce1"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Workshop" sheetId="20" r:id="Rb5713055d8f04258"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Guest Lecture - GLIT" sheetId="21" r:id="R12dd0b22f0dc461f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Industrial Visit - IV" sheetId="22" r:id="R43cd131aa5da4c26"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Internship - Placement" sheetId="23" r:id="Rc61fca62683e4c40"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="MoU - MoU Signing" sheetId="24" r:id="Rb4d33ff4bc9a48e3"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="New Data Added" sheetId="25" r:id="R00a58db3d7854321"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Planned - Section 4" sheetId="26" r:id="Rabfb1e31dd4241c1"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Planned Activities" sheetId="27" r:id="Rf52ff2497fcf4119"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Remote Activities" sheetId="28" r:id="Rade993eb4b034e58"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="64 Submission Reconciliation" sheetId="29" r:id="R55a5037ce846417a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" r:id="Rb26a85e0027c4f14"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="All Separated Activities" sheetId="2" r:id="Rde1075e427d64361"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Alumni Talk - Mentoring" sheetId="3" r:id="R2c3a43111e8f4981"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Community Engagement" sheetId="4" r:id="R0bd6726cee41412b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Conference" sheetId="5" r:id="R031663aeae1f4a74"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Curriculum Feedback Session" sheetId="6" r:id="R3d8220c287ee48cc"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="GLIT" sheetId="7" r:id="R0890c33234904a36"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Guest Lecture" sheetId="8" r:id="R07c1dea3ba6b4c16"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IAB Meeting - Industry Consulta" sheetId="9" r:id="R4548b582a5524df0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IP" sheetId="10" r:id="Rec7a0fa7542b4f29"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IV" sheetId="11" r:id="Rb52201a427304165"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Industrial Visit" sheetId="12" r:id="R22def7a21bdc4faf"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Internship-Placement" sheetId="13" r:id="Rebcb8e17359b4b1b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="MOU" sheetId="14" r:id="Ra6ba3f1c96274bd0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="MoU Signing (Memorandum of Unde" sheetId="15" r:id="Rfa5447222745496d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Others" sheetId="16" r:id="R3ec50d0ecb2040fb"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Research Collaboration" sheetId="17" r:id="Rcdaec88ea94a439e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Seminar" sheetId="18" r:id="Rf02d67acf91f4f5d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Unclassified" sheetId="19" r:id="R70fbac74cacc4598"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Workshop" sheetId="20" r:id="R282eee770b9f4876"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Guest Lecture - GLIT" sheetId="21" r:id="R489ae41136394f49"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Industrial Visit - IV" sheetId="22" r:id="R307235be8ad146dc"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Internship - Placement" sheetId="23" r:id="Ref66f0af73dd466f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="MoU - MoU Signing" sheetId="24" r:id="R40658b60fcad49d6"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="New Data Added" sheetId="25" r:id="Rb2ef36d44cf14f5b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Planned - Section 4" sheetId="26" r:id="R5f3ee96c62184902"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Planned Activities" sheetId="27" r:id="Rb22d8e80820a49ba"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Remote Activities" sheetId="28" r:id="R8b7a58f700014271"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="64 Submission Reconciliation" sheetId="29" r:id="R0b477f7b04a94d95"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -1926,7 +1926,7 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="C2" s="8" t="n">
-        <x:v>598</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="E2" s="22" t="str">
         <x:v>Internship / Placement (excluding Planned)</x:v>
@@ -18596,8 +18596,8 @@
       <x:c r="L75" s="2" t="str">
         <x:v>Alumni Talk / Mentoring</x:v>
       </x:c>
-      <x:c r="M75" s="2" t="str">
-        <x:v>590</x:v>
+      <x:c r="M75" s="2" t="n">
+        <x:v>1</x:v>
       </x:c>
       <x:c r="N75" s="2" t="str">
         <x:v>...</x:v>
@@ -47824,8 +47824,8 @@
       <x:c r="L2" s="2" t="str">
         <x:v>Alumni Talk / Mentoring</x:v>
       </x:c>
-      <x:c r="M2" s="2" t="str">
-        <x:v>590</x:v>
+      <x:c r="M2" s="2" t="n">
+        <x:v>1</x:v>
       </x:c>
       <x:c r="N2" s="2" t="str">
         <x:v>...</x:v>

--- a/data/UOL_Separated_All_Activity_Data_Cleaned.xlsx
+++ b/data/UOL_Separated_All_Activity_Data_Cleaned.xlsx
@@ -2,35 +2,35 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" r:id="Rb26a85e0027c4f14"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="All Separated Activities" sheetId="2" r:id="Rde1075e427d64361"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Alumni Talk - Mentoring" sheetId="3" r:id="R2c3a43111e8f4981"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Community Engagement" sheetId="4" r:id="R0bd6726cee41412b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Conference" sheetId="5" r:id="R031663aeae1f4a74"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Curriculum Feedback Session" sheetId="6" r:id="R3d8220c287ee48cc"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="GLIT" sheetId="7" r:id="R0890c33234904a36"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Guest Lecture" sheetId="8" r:id="R07c1dea3ba6b4c16"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IAB Meeting - Industry Consulta" sheetId="9" r:id="R4548b582a5524df0"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IP" sheetId="10" r:id="Rec7a0fa7542b4f29"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IV" sheetId="11" r:id="Rb52201a427304165"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Industrial Visit" sheetId="12" r:id="R22def7a21bdc4faf"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Internship-Placement" sheetId="13" r:id="Rebcb8e17359b4b1b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="MOU" sheetId="14" r:id="Ra6ba3f1c96274bd0"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="MoU Signing (Memorandum of Unde" sheetId="15" r:id="Rfa5447222745496d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Others" sheetId="16" r:id="R3ec50d0ecb2040fb"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Research Collaboration" sheetId="17" r:id="Rcdaec88ea94a439e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Seminar" sheetId="18" r:id="Rf02d67acf91f4f5d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Unclassified" sheetId="19" r:id="R70fbac74cacc4598"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Workshop" sheetId="20" r:id="R282eee770b9f4876"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Guest Lecture - GLIT" sheetId="21" r:id="R489ae41136394f49"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Industrial Visit - IV" sheetId="22" r:id="R307235be8ad146dc"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Internship - Placement" sheetId="23" r:id="Ref66f0af73dd466f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="MoU - MoU Signing" sheetId="24" r:id="R40658b60fcad49d6"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="New Data Added" sheetId="25" r:id="Rb2ef36d44cf14f5b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Planned - Section 4" sheetId="26" r:id="R5f3ee96c62184902"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Planned Activities" sheetId="27" r:id="Rb22d8e80820a49ba"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Remote Activities" sheetId="28" r:id="R8b7a58f700014271"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="64 Submission Reconciliation" sheetId="29" r:id="R0b477f7b04a94d95"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" r:id="R53663f30b6b04d29"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="All Separated Activities" sheetId="2" r:id="R383ba04826004b2a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Alumni Talk - Mentoring" sheetId="3" r:id="R78a4deec65ed4d8c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Community Engagement" sheetId="4" r:id="Re20df4e557d94a3d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Conference" sheetId="5" r:id="R144c6048616743e9"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Curriculum Feedback Session" sheetId="6" r:id="R8d9b5be4404f4515"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="GLIT" sheetId="7" r:id="R88345baa6a68416e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Guest Lecture" sheetId="8" r:id="Rd5d0ce7a0253475c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IAB Meeting - Industry Consulta" sheetId="9" r:id="R3ce16af0acdd4169"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IP" sheetId="10" r:id="R3aa3c195c3f54bdd"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IV" sheetId="11" r:id="Rea7888a1311540db"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Industrial Visit" sheetId="12" r:id="Rbb9e16e22b254786"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Internship-Placement" sheetId="13" r:id="R8b51878bf4494ab2"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="MOU" sheetId="14" r:id="Ree5e957172b94559"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="MoU Signing (Memorandum of Unde" sheetId="15" r:id="R0824482cdb4d4052"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Others" sheetId="16" r:id="Rc2ee6de9353a43f6"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Research Collaboration" sheetId="17" r:id="Rc5390336ada2472f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Seminar" sheetId="18" r:id="R60dc99efab224fd1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Unclassified" sheetId="19" r:id="Re3902d4d69824682"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Workshop" sheetId="20" r:id="R9fd6446eab40490d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Guest Lecture - GLIT" sheetId="21" r:id="Rba995d157bcf42e3"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Industrial Visit - IV" sheetId="22" r:id="R2918b379f2db4cc2"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Internship - Placement" sheetId="23" r:id="Ra5946c013c574ab6"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="MoU - MoU Signing" sheetId="24" r:id="Rf20237d5fc0f4761"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="New Data Added" sheetId="25" r:id="R5b47afe481054749"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Planned - Section 4" sheetId="26" r:id="R9ca4bb27e3cb4eeb"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Planned Activities" sheetId="27" r:id="R5f47ae530cce4d33"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Remote Activities" sheetId="28" r:id="R468a8826ec804e63"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="64 Submission Reconciliation" sheetId="29" r:id="Rac58602800724acf"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -1926,7 +1926,7 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="C2" s="8" t="n">
-        <x:v>9</x:v>
+        <x:v>598</x:v>
       </x:c>
       <x:c r="E2" s="22" t="str">
         <x:v>Internship / Placement (excluding Planned)</x:v>
@@ -18597,7 +18597,7 @@
         <x:v>Alumni Talk / Mentoring</x:v>
       </x:c>
       <x:c r="M75" s="2" t="n">
-        <x:v>1</x:v>
+        <x:v>590</x:v>
       </x:c>
       <x:c r="N75" s="2" t="str">
         <x:v>...</x:v>
@@ -47825,7 +47825,7 @@
         <x:v>Alumni Talk / Mentoring</x:v>
       </x:c>
       <x:c r="M2" s="2" t="n">
-        <x:v>1</x:v>
+        <x:v>590</x:v>
       </x:c>
       <x:c r="N2" s="2" t="str">
         <x:v>...</x:v>
